--- a/data/output/sim_gridrnd/ABS1/group_500_40/results/ABS1_G5_results_summary.xlsx
+++ b/data/output/sim_gridrnd/ABS1/group_500_40/results/ABS1_G5_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,367 +466,422 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
@@ -840,10 +895,10 @@
         <v>499</v>
       </c>
       <c r="C2" t="n">
+        <v>59.30318754633062</v>
+      </c>
+      <c r="D2" t="n">
         <v>40</v>
-      </c>
-      <c r="D2" t="n">
-        <v>59.30318754633062</v>
       </c>
       <c r="E2" t="n">
         <v>499</v>
@@ -852,244 +907,277 @@
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>75</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>499.0399553456168</v>
-      </c>
-      <c r="J2" t="n">
-        <v>23.24294631185318</v>
-      </c>
-      <c r="K2" t="n">
-        <v>508.1953237605318</v>
-      </c>
-      <c r="L2" t="n">
-        <v>41.64075607519928</v>
-      </c>
-      <c r="M2" t="n">
-        <v>512.5591017789309</v>
-      </c>
-      <c r="N2" t="n">
-        <v>42.64800859036219</v>
-      </c>
-      <c r="O2" t="n">
-        <v>505.4882645028993</v>
-      </c>
-      <c r="P2" t="n">
-        <v>43.77554696793086</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>501.7898282566257</v>
-      </c>
       <c r="R2" t="n">
-        <v>43.63281882977073</v>
+        <v>499.04</v>
       </c>
       <c r="S2" t="n">
-        <v>500.969263291066</v>
+        <v>23.24</v>
       </c>
       <c r="T2" t="n">
-        <v>42.64008353046422</v>
+        <v>508.2</v>
       </c>
       <c r="U2" t="n">
-        <v>502.281478179475</v>
+        <v>41.64</v>
       </c>
       <c r="V2" t="n">
-        <v>46.50764338502461</v>
+        <v>512.5599999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>502.4372252904702</v>
+        <v>42.65</v>
       </c>
       <c r="X2" t="n">
-        <v>48.07609115717271</v>
+        <v>505.49</v>
       </c>
       <c r="Y2" t="n">
-        <v>502.3574630391295</v>
+        <v>43.78</v>
       </c>
       <c r="Z2" t="n">
-        <v>48.41376909195309</v>
+        <v>501.79</v>
       </c>
       <c r="AA2" t="n">
+        <v>43.63</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>500.97</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>42.64</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>502.28</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>46.51</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>502.44</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>48.08</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>502.36</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>48.41</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>0</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AK2" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AL2" t="n">
         <v>0.175</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AM2" t="n">
         <v>0.08</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AN2" t="n">
         <v>0.06666666666666667</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AO2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AP2" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AQ2" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AR2" t="n">
         <v>0.03</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AS2" t="n">
         <v>495.9</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AT2" t="n">
         <v>506.4</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AU2" t="n">
         <v>510.95</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AV2" t="n">
         <v>506.69</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AW2" t="n">
         <v>506</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AX2" t="n">
         <v>505.7571428571429</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AY2" t="n">
         <v>504.33125</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AZ2" t="n">
         <v>503.2888888888889</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="BA2" t="n">
         <v>503.11</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="BB2" t="n">
         <v>38.72131196124429</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="BC2" t="n">
         <v>44.64982269468342</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="BD2" t="n">
         <v>46.36267356397817</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="BE2" t="n">
         <v>46.96013096233867</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="BF2" t="n">
         <v>46.81381562459242</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="BG2" t="n">
         <v>46.33956523449966</v>
       </c>
-      <c r="AY2" t="n">
+      <c r="BH2" t="n">
         <v>46.43607459117857</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BI2" t="n">
         <v>46.61419536875589</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BJ2" t="n">
         <v>47.41727427847366</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BK2" t="n">
         <v>351</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BL2" t="n">
         <v>351</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="BM2" t="n">
         <v>351</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="BN2" t="n">
         <v>351</v>
       </c>
-      <c r="BF2" t="n">
+      <c r="BO2" t="n">
         <v>351</v>
       </c>
-      <c r="BG2" t="n">
+      <c r="BP2" t="n">
         <v>351</v>
       </c>
-      <c r="BH2" t="n">
+      <c r="BQ2" t="n">
         <v>351</v>
       </c>
-      <c r="BI2" t="n">
+      <c r="BR2" t="n">
         <v>351</v>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BS2" t="n">
         <v>351</v>
       </c>
-      <c r="BK2" t="n">
+      <c r="BT2" t="n">
         <v>554</v>
       </c>
-      <c r="BL2" t="n">
+      <c r="BU2" t="n">
         <v>586</v>
       </c>
-      <c r="BM2" t="n">
+      <c r="BV2" t="n">
         <v>586</v>
       </c>
-      <c r="BN2" t="n">
+      <c r="BW2" t="n">
         <v>586</v>
       </c>
-      <c r="BO2" t="n">
+      <c r="BX2" t="n">
         <v>586</v>
       </c>
-      <c r="BP2" t="n">
+      <c r="BY2" t="n">
         <v>586</v>
       </c>
-      <c r="BQ2" t="n">
+      <c r="BZ2" t="n">
         <v>586</v>
       </c>
-      <c r="BR2" t="n">
+      <c r="CA2" t="n">
         <v>586</v>
       </c>
-      <c r="BS2" t="n">
+      <c r="CB2" t="n">
         <v>586</v>
       </c>
-      <c r="BT2" t="n">
+      <c r="CC2" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BU2" t="n">
+      <c r="CD2" t="n">
         <v>0.875</v>
       </c>
-      <c r="BV2" t="n">
+      <c r="CE2" t="n">
         <v>1</v>
       </c>
-      <c r="BW2" t="n">
+      <c r="CF2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BX2" t="n">
+      <c r="CG2" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="BY2" t="n">
+      <c r="CH2" t="n">
         <v>0.8076923076923077</v>
       </c>
-      <c r="BZ2" t="n">
+      <c r="CI2" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="CA2" t="n">
+      <c r="CJ2" t="n">
         <v>0.9117647058823529</v>
       </c>
-      <c r="CB2" t="n">
+      <c r="CK2" t="n">
         <v>0.918918918918919</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>502.36</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>48.41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S03_G5_499_40_ABS1</t>
+          <t>S02_G5_499_40_ABS1</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>499</v>
       </c>
       <c r="C3" t="n">
+        <v>59.30318754633062</v>
+      </c>
+      <c r="D3" t="n">
         <v>40</v>
-      </c>
-      <c r="D3" t="n">
-        <v>59.30318754633062</v>
       </c>
       <c r="E3" t="n">
         <v>499</v>
@@ -1098,244 +1186,277 @@
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>514.6545059015784</v>
-      </c>
-      <c r="J3" t="n">
-        <v>68.81045360904635</v>
-      </c>
-      <c r="K3" t="n">
-        <v>514.4266802032195</v>
-      </c>
-      <c r="L3" t="n">
-        <v>63.48187831929909</v>
-      </c>
-      <c r="M3" t="n">
-        <v>515.9675689760546</v>
-      </c>
-      <c r="N3" t="n">
-        <v>53.58148163373682</v>
-      </c>
-      <c r="O3" t="n">
-        <v>509.1934720589991</v>
-      </c>
-      <c r="P3" t="n">
-        <v>51.5743434215144</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>508.3960505609591</v>
-      </c>
       <c r="R3" t="n">
-        <v>49.86552834896509</v>
+        <v>497.98</v>
       </c>
       <c r="S3" t="n">
-        <v>508.0603961744914</v>
+        <v>61.29</v>
       </c>
       <c r="T3" t="n">
-        <v>51.6084379823955</v>
+        <v>498.05</v>
       </c>
       <c r="U3" t="n">
-        <v>503.6521571660969</v>
+        <v>59.49</v>
       </c>
       <c r="V3" t="n">
-        <v>57.61288418135991</v>
+        <v>496.88</v>
       </c>
       <c r="W3" t="n">
-        <v>502.4786898880111</v>
+        <v>59.73</v>
       </c>
       <c r="X3" t="n">
-        <v>60.11355551932833</v>
+        <v>499.48</v>
       </c>
       <c r="Y3" t="n">
-        <v>504.5630542777648</v>
+        <v>56.99</v>
       </c>
       <c r="Z3" t="n">
-        <v>59.19879217328138</v>
+        <v>503.44</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.15</v>
+        <v>56.38</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1</v>
+        <v>501.45</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.05</v>
+        <v>52.69</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.08</v>
+        <v>503.85</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.08333333333333333</v>
+        <v>52.07</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.07142857142857142</v>
+        <v>497.09</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0125</v>
+        <v>50.57</v>
       </c>
       <c r="AH3" t="n">
+        <v>495.96</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>50.39</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>0</v>
       </c>
-      <c r="AI3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>513.3</v>
-      </c>
       <c r="AK3" t="n">
-        <v>513.4666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>512.3</v>
+        <v>-0.025</v>
       </c>
       <c r="AM3" t="n">
-        <v>513.1900000000001</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>513.3416666666667</v>
+        <v>-0.01666666666666667</v>
       </c>
       <c r="AO3" t="n">
-        <v>512.4285714285714</v>
+        <v>-0.01428571428571429</v>
       </c>
       <c r="AP3" t="n">
-        <v>508.35</v>
+        <v>-0.025</v>
       </c>
       <c r="AQ3" t="n">
-        <v>506.8166666666667</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>507.04</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>62.06013213005593</v>
+        <v>497.95</v>
       </c>
       <c r="AT3" t="n">
-        <v>63.18292666711652</v>
+        <v>498.05</v>
       </c>
       <c r="AU3" t="n">
-        <v>62.45726539002489</v>
+        <v>497.3</v>
       </c>
       <c r="AV3" t="n">
-        <v>58.96536186609898</v>
+        <v>499.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>57.19826568369204</v>
+        <v>499.3833333333333</v>
       </c>
       <c r="AX3" t="n">
-        <v>55.15551298143185</v>
+        <v>499.8642857142857</v>
       </c>
       <c r="AY3" t="n">
-        <v>55.88931024802507</v>
+        <v>499.63125</v>
       </c>
       <c r="AZ3" t="n">
-        <v>57.11367563416352</v>
+        <v>500.9166666666667</v>
       </c>
       <c r="BA3" t="n">
-        <v>57.60146178700676</v>
+        <v>500.55</v>
       </c>
       <c r="BB3" t="n">
-        <v>360</v>
+        <v>60.37919757664887</v>
       </c>
       <c r="BC3" t="n">
-        <v>360</v>
+        <v>63.12089590618941</v>
       </c>
       <c r="BD3" t="n">
-        <v>360</v>
+        <v>61.70725241006927</v>
       </c>
       <c r="BE3" t="n">
-        <v>360</v>
+        <v>61.93633828375714</v>
       </c>
       <c r="BF3" t="n">
-        <v>360</v>
+        <v>59.78296626594867</v>
       </c>
       <c r="BG3" t="n">
-        <v>360</v>
+        <v>58.21980648668406</v>
       </c>
       <c r="BH3" t="n">
-        <v>360</v>
+        <v>56.71029689075433</v>
       </c>
       <c r="BI3" t="n">
-        <v>360</v>
+        <v>55.56006509475428</v>
       </c>
       <c r="BJ3" t="n">
-        <v>360</v>
+        <v>54.4236851012498</v>
       </c>
       <c r="BK3" t="n">
-        <v>600</v>
+        <v>366</v>
       </c>
       <c r="BL3" t="n">
-        <v>600</v>
+        <v>366</v>
       </c>
       <c r="BM3" t="n">
-        <v>600</v>
+        <v>366</v>
       </c>
       <c r="BN3" t="n">
-        <v>600</v>
+        <v>366</v>
       </c>
       <c r="BO3" t="n">
-        <v>600</v>
+        <v>366</v>
       </c>
       <c r="BP3" t="n">
-        <v>600</v>
+        <v>366</v>
       </c>
       <c r="BQ3" t="n">
-        <v>600</v>
+        <v>366</v>
       </c>
       <c r="BR3" t="n">
-        <v>600</v>
+        <v>366</v>
       </c>
       <c r="BS3" t="n">
-        <v>600</v>
+        <v>366</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.6666666666666666</v>
+        <v>584</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.3636363636363636</v>
+        <v>584</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.2666666666666667</v>
+        <v>584</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.8823529411764706</v>
+        <v>584</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.95</v>
+        <v>584</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.7916666666666666</v>
+        <v>584</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.7777777777777778</v>
+        <v>584</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.8888888888888888</v>
+        <v>584</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.9310344827586207</v>
+        <v>584</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>495.96</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>50.39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S02_G5_499_40_ABS1</t>
+          <t>S03_G5_499_40_ABS1</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>499</v>
       </c>
       <c r="C4" t="n">
+        <v>59.30318754633062</v>
+      </c>
+      <c r="D4" t="n">
         <v>40</v>
-      </c>
-      <c r="D4" t="n">
-        <v>59.30318754633062</v>
       </c>
       <c r="E4" t="n">
         <v>499</v>
@@ -1344,720 +1465,819 @@
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>75.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>497.9757343854174</v>
-      </c>
-      <c r="J4" t="n">
-        <v>61.28744040173832</v>
-      </c>
-      <c r="K4" t="n">
-        <v>498.0480392177103</v>
-      </c>
-      <c r="L4" t="n">
-        <v>59.48510624484889</v>
-      </c>
-      <c r="M4" t="n">
-        <v>496.8769321071923</v>
-      </c>
-      <c r="N4" t="n">
-        <v>59.72892725043825</v>
-      </c>
-      <c r="O4" t="n">
-        <v>499.4796708528261</v>
-      </c>
-      <c r="P4" t="n">
-        <v>56.99339090950576</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>503.4437492928701</v>
-      </c>
       <c r="R4" t="n">
-        <v>56.37882616486364</v>
+        <v>514.65</v>
       </c>
       <c r="S4" t="n">
-        <v>501.4521823202521</v>
+        <v>68.81</v>
       </c>
       <c r="T4" t="n">
-        <v>52.69117602559839</v>
+        <v>514.4299999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>503.8509165028302</v>
+        <v>63.48</v>
       </c>
       <c r="V4" t="n">
-        <v>52.06765735912447</v>
+        <v>515.97</v>
       </c>
       <c r="W4" t="n">
-        <v>497.0881982984229</v>
+        <v>53.58</v>
       </c>
       <c r="X4" t="n">
-        <v>50.57131721904106</v>
+        <v>509.19</v>
       </c>
       <c r="Y4" t="n">
-        <v>495.9638428984645</v>
+        <v>51.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>50.38918856111611</v>
+        <v>508.4</v>
       </c>
       <c r="AA4" t="n">
+        <v>49.87</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>508.06</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>51.61</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>503.65</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>57.61</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>502.48</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>60.11</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>504.56</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>0</v>
       </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-0.025</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-0.01666666666666667</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-0.01428571428571429</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-0.025</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>497.95</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>498.05</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>497.3</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>499.5</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>499.3833333333333</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>499.8642857142857</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>499.63125</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>500.9166666666667</v>
-      </c>
       <c r="AR4" t="n">
-        <v>500.55</v>
+        <v>0.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>60.37919757664887</v>
+        <v>513.3</v>
       </c>
       <c r="AT4" t="n">
-        <v>63.12089590618941</v>
+        <v>513.4666666666667</v>
       </c>
       <c r="AU4" t="n">
-        <v>61.70725241006927</v>
+        <v>512.3</v>
       </c>
       <c r="AV4" t="n">
-        <v>61.93633828375714</v>
+        <v>513.1900000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>59.78296626594867</v>
+        <v>513.3416666666667</v>
       </c>
       <c r="AX4" t="n">
-        <v>58.21980648668406</v>
+        <v>512.4285714285714</v>
       </c>
       <c r="AY4" t="n">
-        <v>56.71029689075433</v>
+        <v>508.35</v>
       </c>
       <c r="AZ4" t="n">
-        <v>55.56006509475428</v>
+        <v>506.8166666666667</v>
       </c>
       <c r="BA4" t="n">
-        <v>54.4236851012498</v>
+        <v>507.04</v>
       </c>
       <c r="BB4" t="n">
-        <v>366</v>
+        <v>62.06013213005593</v>
       </c>
       <c r="BC4" t="n">
-        <v>366</v>
+        <v>63.18292666711652</v>
       </c>
       <c r="BD4" t="n">
-        <v>366</v>
+        <v>62.45726539002489</v>
       </c>
       <c r="BE4" t="n">
-        <v>366</v>
+        <v>58.96536186609898</v>
       </c>
       <c r="BF4" t="n">
-        <v>366</v>
+        <v>57.19826568369204</v>
       </c>
       <c r="BG4" t="n">
-        <v>366</v>
+        <v>55.15551298143185</v>
       </c>
       <c r="BH4" t="n">
-        <v>366</v>
+        <v>55.88931024802507</v>
       </c>
       <c r="BI4" t="n">
-        <v>366</v>
+        <v>57.11367563416352</v>
       </c>
       <c r="BJ4" t="n">
-        <v>366</v>
+        <v>57.60146178700676</v>
       </c>
       <c r="BK4" t="n">
-        <v>584</v>
+        <v>360</v>
       </c>
       <c r="BL4" t="n">
-        <v>584</v>
+        <v>360</v>
       </c>
       <c r="BM4" t="n">
-        <v>584</v>
+        <v>360</v>
       </c>
       <c r="BN4" t="n">
-        <v>584</v>
+        <v>360</v>
       </c>
       <c r="BO4" t="n">
-        <v>584</v>
+        <v>360</v>
       </c>
       <c r="BP4" t="n">
-        <v>584</v>
+        <v>360</v>
       </c>
       <c r="BQ4" t="n">
-        <v>584</v>
+        <v>360</v>
       </c>
       <c r="BR4" t="n">
-        <v>584</v>
+        <v>360</v>
       </c>
       <c r="BS4" t="n">
-        <v>584</v>
+        <v>360</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.8333333333333334</v>
+        <v>600</v>
       </c>
       <c r="BU4" t="n">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.8666666666666667</v>
+        <v>600</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.875</v>
+        <v>600</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.9444444444444444</v>
+        <v>600</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.9523809523809523</v>
+        <v>600</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.9230769230769231</v>
+        <v>600</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.84375</v>
+        <v>600</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.9310344827586207</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>504.56</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>59.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S05_G5_500_41_ABS1</t>
+          <t>S04_G5_499_42_ABS1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C5" t="n">
-        <v>41</v>
+        <v>62.26834692364714</v>
       </c>
       <c r="D5" t="n">
-        <v>60.78576723498888</v>
+        <v>42</v>
       </c>
       <c r="E5" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F5" t="n">
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>490.7538523457235</v>
-      </c>
-      <c r="J5" t="n">
-        <v>70.48167897519957</v>
-      </c>
-      <c r="K5" t="n">
-        <v>485.1156089927284</v>
-      </c>
-      <c r="L5" t="n">
-        <v>72.82367237275571</v>
-      </c>
-      <c r="M5" t="n">
-        <v>493.8750986752531</v>
-      </c>
-      <c r="N5" t="n">
-        <v>62.69539641989743</v>
-      </c>
-      <c r="O5" t="n">
-        <v>496.7827343130973</v>
-      </c>
-      <c r="P5" t="n">
-        <v>56.60246298534346</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>503.1661976005961</v>
-      </c>
       <c r="R5" t="n">
-        <v>58.26448653292294</v>
+        <v>482.97</v>
       </c>
       <c r="S5" t="n">
-        <v>503.3388593267383</v>
+        <v>51.71</v>
       </c>
       <c r="T5" t="n">
-        <v>56.80552392908857</v>
+        <v>488.11</v>
       </c>
       <c r="U5" t="n">
-        <v>503.6600516435606</v>
+        <v>30.15</v>
       </c>
       <c r="V5" t="n">
-        <v>53.94765379557003</v>
+        <v>493.06</v>
       </c>
       <c r="W5" t="n">
-        <v>506.1609893987302</v>
+        <v>38.5</v>
       </c>
       <c r="X5" t="n">
-        <v>52.96807183253438</v>
+        <v>494.97</v>
       </c>
       <c r="Y5" t="n">
-        <v>506.4781125537206</v>
+        <v>44.51</v>
       </c>
       <c r="Z5" t="n">
-        <v>51.74654525300423</v>
+        <v>492.28</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>37.76</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.06666666666666667</v>
+        <v>490.76</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.05</v>
+        <v>36.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.1</v>
+        <v>490.86</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.08333333333333333</v>
+        <v>35.89</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.05714285714285714</v>
+        <v>490.46</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.075</v>
+        <v>37.34</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.1</v>
+        <v>492.62</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.09</v>
+        <v>37.26</v>
       </c>
       <c r="AJ5" t="n">
-        <v>490.95</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AK5" t="n">
-        <v>486</v>
+        <v>-0.3559322033898305</v>
       </c>
       <c r="AL5" t="n">
-        <v>487.8875</v>
+        <v>-0.2151898734177215</v>
       </c>
       <c r="AM5" t="n">
-        <v>487.97</v>
+        <v>-0.1111111111111111</v>
       </c>
       <c r="AN5" t="n">
-        <v>491.125</v>
+        <v>-0.07563025210084033</v>
       </c>
       <c r="AO5" t="n">
-        <v>494.6571428571428</v>
+        <v>-0.07913669064748201</v>
       </c>
       <c r="AP5" t="n">
-        <v>495.05</v>
+        <v>-0.08176100628930817</v>
       </c>
       <c r="AQ5" t="n">
-        <v>495.0055555555555</v>
+        <v>-0.07262569832402235</v>
       </c>
       <c r="AR5" t="n">
-        <v>496.48</v>
+        <v>-0.05527638190954774</v>
       </c>
       <c r="AS5" t="n">
-        <v>53.06031944871798</v>
+        <v>488.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>62.52306241166801</v>
+        <v>482.4666666666666</v>
       </c>
       <c r="AU5" t="n">
-        <v>65.51011253043303</v>
+        <v>487.6875</v>
       </c>
       <c r="AV5" t="n">
-        <v>63.24499268716852</v>
+        <v>491.66</v>
       </c>
       <c r="AW5" t="n">
-        <v>61.72014291677124</v>
+        <v>492.2666666666667</v>
       </c>
       <c r="AX5" t="n">
-        <v>61.15084060029305</v>
+        <v>492.0571428571429</v>
       </c>
       <c r="AY5" t="n">
-        <v>59.51772845127743</v>
+        <v>491.075</v>
       </c>
       <c r="AZ5" t="n">
-        <v>57.78210961325334</v>
+        <v>490.6833333333333</v>
       </c>
       <c r="BA5" t="n">
-        <v>56.74838852337571</v>
+        <v>491.05</v>
       </c>
       <c r="BB5" t="n">
-        <v>398</v>
+        <v>37.9321763151022</v>
       </c>
       <c r="BC5" t="n">
-        <v>395</v>
+        <v>43.04434405999882</v>
       </c>
       <c r="BD5" t="n">
-        <v>395</v>
+        <v>41.97516937130808</v>
       </c>
       <c r="BE5" t="n">
-        <v>395</v>
+        <v>42.31647905958151</v>
       </c>
       <c r="BF5" t="n">
-        <v>395</v>
+        <v>42.60198221783687</v>
       </c>
       <c r="BG5" t="n">
-        <v>395</v>
+        <v>41.96065698596576</v>
       </c>
       <c r="BH5" t="n">
-        <v>395</v>
+        <v>41.26038505637096</v>
       </c>
       <c r="BI5" t="n">
-        <v>395</v>
+        <v>40.45223177471863</v>
       </c>
       <c r="BJ5" t="n">
-        <v>395</v>
+        <v>40.00021874940186</v>
       </c>
       <c r="BK5" t="n">
-        <v>636</v>
+        <v>418</v>
       </c>
       <c r="BL5" t="n">
-        <v>636</v>
+        <v>400</v>
       </c>
       <c r="BM5" t="n">
-        <v>636</v>
+        <v>400</v>
       </c>
       <c r="BN5" t="n">
-        <v>636</v>
+        <v>400</v>
       </c>
       <c r="BO5" t="n">
-        <v>636</v>
+        <v>400</v>
       </c>
       <c r="BP5" t="n">
-        <v>636</v>
+        <v>400</v>
       </c>
       <c r="BQ5" t="n">
-        <v>636</v>
+        <v>400</v>
       </c>
       <c r="BR5" t="n">
-        <v>636</v>
+        <v>400</v>
       </c>
       <c r="BS5" t="n">
-        <v>636</v>
+        <v>400</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.5714285714285714</v>
+        <v>638</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.7142857142857143</v>
+        <v>638</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.9</v>
+        <v>638</v>
       </c>
       <c r="BW5" t="n">
+        <v>638</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>638</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>638</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>638</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>638</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>638</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="CE5" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="BX5" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>0.8636363636363636</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>0.9565217391304348</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0.8928571428571429</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>0.9354838709677419</v>
+      <c r="CF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.4193548387096774</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>492.62</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>37.26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S04_G5_499_42_ABS1</t>
+          <t>S05_G5_500_41_ABS1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C6" t="n">
-        <v>42</v>
+        <v>60.78576723498888</v>
       </c>
       <c r="D6" t="n">
-        <v>62.26834692364714</v>
+        <v>41</v>
       </c>
       <c r="E6" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F6" t="n">
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>482.9686152898011</v>
-      </c>
-      <c r="J6" t="n">
-        <v>51.71346976330861</v>
-      </c>
-      <c r="K6" t="n">
-        <v>488.112707725708</v>
-      </c>
-      <c r="L6" t="n">
-        <v>30.15244236506418</v>
-      </c>
-      <c r="M6" t="n">
-        <v>493.0555446853714</v>
-      </c>
-      <c r="N6" t="n">
-        <v>38.50091211146332</v>
-      </c>
-      <c r="O6" t="n">
-        <v>494.9738848839741</v>
-      </c>
-      <c r="P6" t="n">
-        <v>44.51285253342174</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>492.2794972483042</v>
-      </c>
       <c r="R6" t="n">
-        <v>37.75795331396712</v>
+        <v>490.75</v>
       </c>
       <c r="S6" t="n">
-        <v>490.7611469610811</v>
+        <v>70.48</v>
       </c>
       <c r="T6" t="n">
-        <v>36.346593012079</v>
+        <v>485.12</v>
       </c>
       <c r="U6" t="n">
-        <v>490.8639921769844</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>35.88525312792942</v>
+        <v>493.88</v>
       </c>
       <c r="W6" t="n">
-        <v>490.4623068453259</v>
+        <v>62.7</v>
       </c>
       <c r="X6" t="n">
-        <v>37.34493350910971</v>
+        <v>496.78</v>
       </c>
       <c r="Y6" t="n">
-        <v>492.6175653419448</v>
+        <v>56.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>37.26372333706139</v>
+        <v>503.17</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.3333333333333333</v>
+        <v>58.26</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.3559322033898305</v>
+        <v>503.34</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.2151898734177215</v>
+        <v>56.81</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.1111111111111111</v>
+        <v>503.66</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.07563025210084033</v>
+        <v>53.95</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.07913669064748201</v>
+        <v>506.16</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.08176100628930817</v>
+        <v>52.97</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.07262569832402235</v>
+        <v>506.48</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.05527638190954774</v>
+        <v>51.75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>488.5</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>482.4666666666666</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="AL6" t="n">
-        <v>487.6875</v>
+        <v>-0.05</v>
       </c>
       <c r="AM6" t="n">
-        <v>491.66</v>
+        <v>-0.1</v>
       </c>
       <c r="AN6" t="n">
-        <v>492.2666666666667</v>
+        <v>-0.08333333333333333</v>
       </c>
       <c r="AO6" t="n">
-        <v>492.0571428571429</v>
+        <v>-0.05714285714285714</v>
       </c>
       <c r="AP6" t="n">
-        <v>491.075</v>
+        <v>-0.075</v>
       </c>
       <c r="AQ6" t="n">
-        <v>490.6833333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="AR6" t="n">
-        <v>491.05</v>
+        <v>-0.09</v>
       </c>
       <c r="AS6" t="n">
-        <v>37.9321763151022</v>
+        <v>490.95</v>
       </c>
       <c r="AT6" t="n">
-        <v>43.04434405999882</v>
+        <v>486</v>
       </c>
       <c r="AU6" t="n">
-        <v>41.97516937130808</v>
+        <v>487.8875</v>
       </c>
       <c r="AV6" t="n">
-        <v>42.31647905958151</v>
+        <v>487.97</v>
       </c>
       <c r="AW6" t="n">
-        <v>42.60198221783687</v>
+        <v>491.125</v>
       </c>
       <c r="AX6" t="n">
-        <v>41.96065698596576</v>
+        <v>494.6571428571428</v>
       </c>
       <c r="AY6" t="n">
-        <v>41.26038505637096</v>
+        <v>495.05</v>
       </c>
       <c r="AZ6" t="n">
-        <v>40.45223177471863</v>
+        <v>495.0055555555555</v>
       </c>
       <c r="BA6" t="n">
-        <v>40.00021874940186</v>
+        <v>496.48</v>
       </c>
       <c r="BB6" t="n">
-        <v>418</v>
+        <v>53.06031944871798</v>
       </c>
       <c r="BC6" t="n">
-        <v>400</v>
+        <v>62.52306241166801</v>
       </c>
       <c r="BD6" t="n">
-        <v>400</v>
+        <v>65.51011253043303</v>
       </c>
       <c r="BE6" t="n">
-        <v>400</v>
+        <v>63.24499268716852</v>
       </c>
       <c r="BF6" t="n">
-        <v>400</v>
+        <v>61.72014291677124</v>
       </c>
       <c r="BG6" t="n">
-        <v>400</v>
+        <v>61.15084060029305</v>
       </c>
       <c r="BH6" t="n">
-        <v>400</v>
+        <v>59.51772845127743</v>
       </c>
       <c r="BI6" t="n">
-        <v>400</v>
+        <v>57.78210961325334</v>
       </c>
       <c r="BJ6" t="n">
-        <v>400</v>
+        <v>56.74838852337571</v>
       </c>
       <c r="BK6" t="n">
-        <v>638</v>
+        <v>398</v>
       </c>
       <c r="BL6" t="n">
-        <v>638</v>
+        <v>395</v>
       </c>
       <c r="BM6" t="n">
-        <v>638</v>
+        <v>395</v>
       </c>
       <c r="BN6" t="n">
-        <v>638</v>
+        <v>395</v>
       </c>
       <c r="BO6" t="n">
-        <v>638</v>
+        <v>395</v>
       </c>
       <c r="BP6" t="n">
-        <v>638</v>
+        <v>395</v>
       </c>
       <c r="BQ6" t="n">
-        <v>638</v>
+        <v>395</v>
       </c>
       <c r="BR6" t="n">
-        <v>638</v>
+        <v>395</v>
       </c>
       <c r="BS6" t="n">
-        <v>638</v>
+        <v>395</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.3333333333333333</v>
+        <v>636</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.6153846153846154</v>
+        <v>636</v>
       </c>
       <c r="BV6" t="n">
+        <v>636</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>636</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>636</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>636</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>636</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>636</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>636</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CF6" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="BW6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>0.8823529411764706</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>0.7391304347826086</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>0.4193548387096774</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>0.3611111111111111</v>
+      <c r="CG6" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.9565217391304348</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.8928571428571429</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>506.48</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>51.75</v>
       </c>
     </row>
     <row r="7">
@@ -2070,10 +2290,10 @@
         <v>501</v>
       </c>
       <c r="C7" t="n">
+        <v>59.30318754633062</v>
+      </c>
+      <c r="D7" t="n">
         <v>40</v>
-      </c>
-      <c r="D7" t="n">
-        <v>59.30318754633062</v>
       </c>
       <c r="E7" t="n">
         <v>501</v>
@@ -2082,228 +2302,261 @@
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>76</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>500.9570128652241</v>
-      </c>
-      <c r="J7" t="n">
-        <v>40.84110354028754</v>
-      </c>
-      <c r="K7" t="n">
-        <v>504.1135083330542</v>
-      </c>
-      <c r="L7" t="n">
-        <v>36.82191727319098</v>
-      </c>
-      <c r="M7" t="n">
-        <v>501.2172073610161</v>
-      </c>
-      <c r="N7" t="n">
-        <v>38.70371433375796</v>
-      </c>
-      <c r="O7" t="n">
-        <v>497.5103849335031</v>
-      </c>
-      <c r="P7" t="n">
-        <v>41.2569517244165</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>497.9356027436438</v>
-      </c>
       <c r="R7" t="n">
-        <v>45.99370015820535</v>
+        <v>500.96</v>
       </c>
       <c r="S7" t="n">
-        <v>501.0141844467127</v>
+        <v>40.84</v>
       </c>
       <c r="T7" t="n">
-        <v>45.202028013749</v>
+        <v>504.11</v>
       </c>
       <c r="U7" t="n">
-        <v>501.2681661322054</v>
+        <v>36.82</v>
       </c>
       <c r="V7" t="n">
-        <v>41.98919970517871</v>
+        <v>501.22</v>
       </c>
       <c r="W7" t="n">
-        <v>498.7690752129197</v>
+        <v>38.7</v>
       </c>
       <c r="X7" t="n">
-        <v>41.25284556826577</v>
+        <v>497.51</v>
       </c>
       <c r="Y7" t="n">
-        <v>497.9664929646686</v>
+        <v>41.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>42.39946282597651</v>
+        <v>497.94</v>
       </c>
       <c r="AA7" t="n">
+        <v>45.99</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>501.01</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>501.27</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>498.77</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>497.97</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>-0.3</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AK7" t="n">
         <v>-0.03333333333333333</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AL7" t="n">
         <v>0</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AM7" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AN7" t="n">
         <v>-0.06666666666666667</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AO7" t="n">
         <v>-0.01428571428571429</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AP7" t="n">
         <v>-0.0125</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AQ7" t="n">
         <v>-0.01111111111111111</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AR7" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AS7" t="n">
         <v>492.375</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AT7" t="n">
         <v>502.6666666666667</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AU7" t="n">
         <v>502.125</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AV7" t="n">
         <v>498.81</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AW7" t="n">
         <v>497.6083333333333</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AX7" t="n">
         <v>500.3642857142857</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AY7" t="n">
         <v>500.6875</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AZ7" t="n">
         <v>500.3333333333333</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="BA7" t="n">
         <v>499.515</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="BB7" t="n">
         <v>39.23562634902112</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="BC7" t="n">
         <v>41.84003930314704</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="BD7" t="n">
         <v>40.71866126237453</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="BE7" t="n">
         <v>41.41900409232458</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="BF7" t="n">
         <v>42.7428933339281</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="BG7" t="n">
         <v>44.69886714996026</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="BH7" t="n">
         <v>44.39132622202225</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BI7" t="n">
         <v>43.82350967232086</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BJ7" t="n">
         <v>43.6037816593928</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BK7" t="n">
         <v>355</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BL7" t="n">
         <v>355</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="BM7" t="n">
         <v>355</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="BN7" t="n">
         <v>355</v>
       </c>
-      <c r="BF7" t="n">
+      <c r="BO7" t="n">
         <v>355</v>
       </c>
-      <c r="BG7" t="n">
+      <c r="BP7" t="n">
         <v>355</v>
       </c>
-      <c r="BH7" t="n">
+      <c r="BQ7" t="n">
         <v>355</v>
       </c>
-      <c r="BI7" t="n">
+      <c r="BR7" t="n">
         <v>355</v>
       </c>
-      <c r="BJ7" t="n">
+      <c r="BS7" t="n">
         <v>355</v>
       </c>
-      <c r="BK7" t="n">
+      <c r="BT7" t="n">
         <v>560</v>
       </c>
-      <c r="BL7" t="n">
+      <c r="BU7" t="n">
         <v>563</v>
       </c>
-      <c r="BM7" t="n">
+      <c r="BV7" t="n">
         <v>563</v>
       </c>
-      <c r="BN7" t="n">
+      <c r="BW7" t="n">
         <v>563</v>
       </c>
-      <c r="BO7" t="n">
+      <c r="BX7" t="n">
         <v>563</v>
       </c>
-      <c r="BP7" t="n">
+      <c r="BY7" t="n">
         <v>565</v>
       </c>
-      <c r="BQ7" t="n">
+      <c r="BZ7" t="n">
         <v>565</v>
       </c>
-      <c r="BR7" t="n">
+      <c r="CA7" t="n">
         <v>565</v>
       </c>
-      <c r="BS7" t="n">
+      <c r="CB7" t="n">
         <v>565</v>
       </c>
-      <c r="BT7" t="n">
+      <c r="CC7" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BU7" t="n">
+      <c r="CD7" t="n">
         <v>1</v>
       </c>
-      <c r="BV7" t="n">
+      <c r="CE7" t="n">
         <v>1</v>
       </c>
-      <c r="BW7" t="n">
+      <c r="CF7" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="BX7" t="n">
+      <c r="CG7" t="n">
         <v>0.85</v>
       </c>
-      <c r="BY7" t="n">
+      <c r="CH7" t="n">
         <v>0.75</v>
       </c>
-      <c r="BZ7" t="n">
+      <c r="CI7" t="n">
         <v>0.8148148148148148</v>
       </c>
-      <c r="CA7" t="n">
+      <c r="CJ7" t="n">
         <v>0.9655172413793104</v>
       </c>
-      <c r="CB7" t="n">
+      <c r="CK7" t="n">
         <v>1</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>497.97</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>42.4</v>
       </c>
     </row>
     <row r="8">
@@ -2316,10 +2569,10 @@
         <v>499</v>
       </c>
       <c r="C8" t="n">
+        <v>59.30318754633062</v>
+      </c>
+      <c r="D8" t="n">
         <v>40</v>
-      </c>
-      <c r="D8" t="n">
-        <v>59.30318754633062</v>
       </c>
       <c r="E8" t="n">
         <v>499</v>
@@ -2328,228 +2581,261 @@
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>506.8426912892507</v>
-      </c>
-      <c r="J8" t="n">
-        <v>16.37140634318924</v>
-      </c>
-      <c r="K8" t="n">
-        <v>503.1822484761853</v>
-      </c>
-      <c r="L8" t="n">
-        <v>27.81128490282747</v>
-      </c>
-      <c r="M8" t="n">
-        <v>502.7423003957347</v>
-      </c>
-      <c r="N8" t="n">
-        <v>42.47082569710867</v>
-      </c>
-      <c r="O8" t="n">
-        <v>510.0298288616498</v>
-      </c>
-      <c r="P8" t="n">
-        <v>57.82058021863848</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>507.6346568824765</v>
-      </c>
       <c r="R8" t="n">
-        <v>57.32933110406876</v>
+        <v>506.84</v>
       </c>
       <c r="S8" t="n">
-        <v>506.3137082734931</v>
+        <v>16.37</v>
       </c>
       <c r="T8" t="n">
-        <v>54.3674847192819</v>
+        <v>503.18</v>
       </c>
       <c r="U8" t="n">
-        <v>508.1675343613884</v>
+        <v>27.81</v>
       </c>
       <c r="V8" t="n">
-        <v>54.83870866277804</v>
+        <v>502.74</v>
       </c>
       <c r="W8" t="n">
-        <v>505.637875739771</v>
+        <v>42.47</v>
       </c>
       <c r="X8" t="n">
-        <v>54.11637592125724</v>
+        <v>510.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>507.1718729363111</v>
+        <v>57.82</v>
       </c>
       <c r="Z8" t="n">
-        <v>50.83573556750691</v>
+        <v>507.63</v>
       </c>
       <c r="AA8" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>506.31</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>54.37</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>508.17</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>505.64</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>54.12</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>507.17</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>50.84</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>0.3157894736842105</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AK8" t="n">
         <v>0.1379310344827586</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AL8" t="n">
         <v>0.05128205128205128</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AM8" t="n">
         <v>0.1836734693877551</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AN8" t="n">
         <v>0.1525423728813559</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AO8" t="n">
         <v>0.1159420289855072</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AP8" t="n">
         <v>0.1265822784810127</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AQ8" t="n">
         <v>0.101123595505618</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AR8" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AS8" t="n">
         <v>507.85</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AT8" t="n">
         <v>503.4</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AU8" t="n">
         <v>501.2</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AV8" t="n">
         <v>512.72</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AW8" t="n">
         <v>511.5666666666667</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AX8" t="n">
         <v>509.7571428571429</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AY8" t="n">
         <v>510.875</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AZ8" t="n">
         <v>509.4666666666666</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="BA8" t="n">
         <v>510.195</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="BB8" t="n">
         <v>32.61253593328799</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BC8" t="n">
         <v>34.49115828730604</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="BD8" t="n">
         <v>37.61229852056372</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="BE8" t="n">
         <v>47.62564015317799</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="BF8" t="n">
         <v>52.80715439744463</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="BG8" t="n">
         <v>54.47251881566014</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BH8" t="n">
         <v>55.06606827257599</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BI8" t="n">
         <v>55.38656074456249</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BJ8" t="n">
         <v>54.62972611133979</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BK8" t="n">
         <v>408</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BL8" t="n">
         <v>408</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BM8" t="n">
         <v>408</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BN8" t="n">
         <v>408</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BO8" t="n">
         <v>408</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BP8" t="n">
         <v>408</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BQ8" t="n">
         <v>408</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BR8" t="n">
         <v>408</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BS8" t="n">
         <v>408</v>
       </c>
-      <c r="BK8" t="n">
+      <c r="BT8" t="n">
         <v>632</v>
       </c>
-      <c r="BL8" t="n">
+      <c r="BU8" t="n">
         <v>632</v>
       </c>
-      <c r="BM8" t="n">
+      <c r="BV8" t="n">
         <v>632</v>
       </c>
-      <c r="BN8" t="n">
+      <c r="BW8" t="n">
         <v>632</v>
       </c>
-      <c r="BO8" t="n">
+      <c r="BX8" t="n">
         <v>632</v>
       </c>
-      <c r="BP8" t="n">
+      <c r="BY8" t="n">
         <v>632</v>
       </c>
-      <c r="BQ8" t="n">
+      <c r="BZ8" t="n">
         <v>632</v>
       </c>
-      <c r="BR8" t="n">
+      <c r="CA8" t="n">
         <v>632</v>
       </c>
-      <c r="BS8" t="n">
+      <c r="CB8" t="n">
         <v>632</v>
       </c>
-      <c r="BT8" t="n">
+      <c r="CC8" t="n">
         <v>0</v>
       </c>
-      <c r="BU8" t="n">
+      <c r="CD8" t="n">
         <v>0</v>
       </c>
-      <c r="BV8" t="n">
+      <c r="CE8" t="n">
         <v>0.9</v>
       </c>
-      <c r="BW8" t="n">
+      <c r="CF8" t="n">
         <v>0.9</v>
       </c>
-      <c r="BX8" t="n">
+      <c r="CG8" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="BY8" t="n">
+      <c r="CH8" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="BZ8" t="n">
+      <c r="CI8" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="CA8" t="n">
+      <c r="CJ8" t="n">
         <v>0.95</v>
       </c>
-      <c r="CB8" t="n">
+      <c r="CK8" t="n">
         <v>1</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>507.17</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>50.84</v>
       </c>
     </row>
     <row r="9">
@@ -2562,10 +2848,10 @@
         <v>501</v>
       </c>
       <c r="C9" t="n">
+        <v>59.30318754633062</v>
+      </c>
+      <c r="D9" t="n">
         <v>40</v>
-      </c>
-      <c r="D9" t="n">
-        <v>59.30318754633062</v>
       </c>
       <c r="E9" t="n">
         <v>501</v>
@@ -2574,228 +2860,261 @@
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>510.9968724176908</v>
-      </c>
-      <c r="J9" t="n">
-        <v>69.13205563154912</v>
-      </c>
-      <c r="K9" t="n">
-        <v>518.6698899544376</v>
-      </c>
-      <c r="L9" t="n">
-        <v>57.33836129674695</v>
-      </c>
-      <c r="M9" t="n">
-        <v>514.0387477327979</v>
-      </c>
-      <c r="N9" t="n">
-        <v>49.20345623870015</v>
-      </c>
-      <c r="O9" t="n">
-        <v>518.4893220943072</v>
-      </c>
-      <c r="P9" t="n">
-        <v>53.05001670019666</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>516.1391240018776</v>
-      </c>
       <c r="R9" t="n">
-        <v>50.61025450914175</v>
+        <v>511</v>
       </c>
       <c r="S9" t="n">
-        <v>511.3628133287165</v>
+        <v>69.13</v>
       </c>
       <c r="T9" t="n">
-        <v>52.42128242960468</v>
+        <v>518.67</v>
       </c>
       <c r="U9" t="n">
-        <v>508.5147593939466</v>
+        <v>57.34</v>
       </c>
       <c r="V9" t="n">
-        <v>50.74354167541107</v>
+        <v>514.04</v>
       </c>
       <c r="W9" t="n">
-        <v>507.3323086840643</v>
+        <v>49.2</v>
       </c>
       <c r="X9" t="n">
-        <v>49.05130205677834</v>
+        <v>518.49</v>
       </c>
       <c r="Y9" t="n">
-        <v>502.5373226856251</v>
+        <v>53.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>50.39751671455988</v>
+        <v>516.14</v>
       </c>
       <c r="AA9" t="n">
+        <v>50.61</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>511.36</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>52.42</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>508.51</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>50.74</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>507.33</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>502.54</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>0</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AK9" t="n">
         <v>0.06666666666666667</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AL9" t="n">
         <v>0.075</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AM9" t="n">
         <v>0.04</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AN9" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AO9" t="n">
         <v>0.01428571428571429</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AP9" t="n">
         <v>0.025</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AQ9" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AR9" t="n">
         <v>0.03</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AS9" t="n">
         <v>512.25</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AT9" t="n">
         <v>514.5833333333334</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AU9" t="n">
         <v>516.525</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AV9" t="n">
         <v>516.12</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AW9" t="n">
         <v>516.1416666666667</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AX9" t="n">
         <v>514.9714285714285</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AY9" t="n">
         <v>514.35625</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AZ9" t="n">
         <v>513.5833333333334</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="BA9" t="n">
         <v>512.75</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="BB9" t="n">
         <v>60.06694182326915</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BC9" t="n">
         <v>60.14795415381049</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="BD9" t="n">
         <v>57.58210985193231</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="BE9" t="n">
         <v>55.46030652637975</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="BF9" t="n">
         <v>54.62482583242002</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="BG9" t="n">
         <v>54.03529836493693</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="BH9" t="n">
         <v>53.53565947980374</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BI9" t="n">
         <v>52.75918824664046</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BJ9" t="n">
         <v>52.16950737739432</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BK9" t="n">
         <v>422</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BL9" t="n">
         <v>422</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BM9" t="n">
         <v>422</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BN9" t="n">
         <v>422</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BO9" t="n">
         <v>422</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BP9" t="n">
         <v>422</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BQ9" t="n">
         <v>422</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BR9" t="n">
         <v>422</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BS9" t="n">
         <v>422</v>
       </c>
-      <c r="BK9" t="n">
+      <c r="BT9" t="n">
         <v>631</v>
       </c>
-      <c r="BL9" t="n">
+      <c r="BU9" t="n">
         <v>631</v>
       </c>
-      <c r="BM9" t="n">
+      <c r="BV9" t="n">
         <v>631</v>
       </c>
-      <c r="BN9" t="n">
+      <c r="BW9" t="n">
         <v>631</v>
       </c>
-      <c r="BO9" t="n">
+      <c r="BX9" t="n">
         <v>631</v>
       </c>
-      <c r="BP9" t="n">
+      <c r="BY9" t="n">
         <v>631</v>
       </c>
-      <c r="BQ9" t="n">
+      <c r="BZ9" t="n">
         <v>631</v>
       </c>
-      <c r="BR9" t="n">
+      <c r="CA9" t="n">
         <v>631</v>
       </c>
-      <c r="BS9" t="n">
+      <c r="CB9" t="n">
         <v>631</v>
       </c>
-      <c r="BT9" t="n">
+      <c r="CC9" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="BU9" t="n">
+      <c r="CD9" t="n">
         <v>1</v>
       </c>
-      <c r="BV9" t="n">
+      <c r="CE9" t="n">
         <v>1</v>
       </c>
-      <c r="BW9" t="n">
+      <c r="CF9" t="n">
         <v>0.8</v>
       </c>
-      <c r="BX9" t="n">
+      <c r="CG9" t="n">
         <v>0.8095238095238095</v>
       </c>
-      <c r="BY9" t="n">
+      <c r="CH9" t="n">
         <v>0.7407407407407407</v>
       </c>
-      <c r="BZ9" t="n">
+      <c r="CI9" t="n">
         <v>0.7931034482758621</v>
       </c>
-      <c r="CA9" t="n">
+      <c r="CJ9" t="n">
         <v>0.8064516129032258</v>
       </c>
-      <c r="CB9" t="n">
+      <c r="CK9" t="n">
         <v>0.8</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>502.54</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>50.4</v>
       </c>
     </row>
     <row r="10">
@@ -2808,10 +3127,10 @@
         <v>498</v>
       </c>
       <c r="C10" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D10" t="n">
         <v>38</v>
-      </c>
-      <c r="D10" t="n">
-        <v>56.33802816901409</v>
       </c>
       <c r="E10" t="n">
         <v>498</v>
@@ -2820,228 +3139,261 @@
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>75.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>488.4115021854539</v>
-      </c>
-      <c r="J10" t="n">
-        <v>32.64831439213158</v>
-      </c>
-      <c r="K10" t="n">
-        <v>481.4487882595201</v>
-      </c>
-      <c r="L10" t="n">
-        <v>35.86856597471559</v>
-      </c>
-      <c r="M10" t="n">
-        <v>485.8883088055795</v>
-      </c>
-      <c r="N10" t="n">
-        <v>42.48195007936788</v>
-      </c>
-      <c r="O10" t="n">
-        <v>482.4284120263589</v>
-      </c>
-      <c r="P10" t="n">
-        <v>41.79680803102001</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>487.2407835388825</v>
-      </c>
       <c r="R10" t="n">
-        <v>42.20521786899238</v>
+        <v>488.41</v>
       </c>
       <c r="S10" t="n">
-        <v>489.1360175406039</v>
+        <v>32.65</v>
       </c>
       <c r="T10" t="n">
-        <v>45.03030373158411</v>
+        <v>481.45</v>
       </c>
       <c r="U10" t="n">
-        <v>493.2734735368108</v>
+        <v>35.87</v>
       </c>
       <c r="V10" t="n">
-        <v>45.03456662509963</v>
+        <v>485.89</v>
       </c>
       <c r="W10" t="n">
-        <v>493.4745107882875</v>
+        <v>42.48</v>
       </c>
       <c r="X10" t="n">
-        <v>43.50284155097256</v>
+        <v>482.43</v>
       </c>
       <c r="Y10" t="n">
-        <v>493.4003926982955</v>
+        <v>41.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>45.23173858717637</v>
+        <v>487.24</v>
       </c>
       <c r="AA10" t="n">
+        <v>42.21</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>489.14</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>45.03</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>493.27</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>45.03</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>493.47</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>493.4</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>45.23</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>-0.3</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AK10" t="n">
         <v>-0.2666666666666667</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AL10" t="n">
         <v>-0.15</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AM10" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AN10" t="n">
         <v>-0.1166666666666667</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AO10" t="n">
         <v>-0.07142857142857142</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AP10" t="n">
         <v>-0.0375</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AQ10" t="n">
         <v>-0.05555555555555555</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AR10" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AS10" t="n">
         <v>494.875</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AT10" t="n">
         <v>486.3</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AU10" t="n">
         <v>488.975</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AV10" t="n">
         <v>487.09</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AW10" t="n">
         <v>486.425</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AX10" t="n">
         <v>488.0928571428572</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AY10" t="n">
         <v>489.63125</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AZ10" t="n">
         <v>489.5055555555555</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BA10" t="n">
         <v>490.63</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="BB10" t="n">
         <v>45.72646252445077</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BC10" t="n">
         <v>46.46658297457791</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BD10" t="n">
         <v>46.23255752172921</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="BE10" t="n">
         <v>46.00697664485246</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="BF10" t="n">
         <v>45.11571464948032</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="BG10" t="n">
         <v>45.2698096225874</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BH10" t="n">
         <v>46.07271723523044</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BI10" t="n">
         <v>46.08777823316215</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BJ10" t="n">
         <v>45.99612048858034</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BK10" t="n">
         <v>426</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BL10" t="n">
         <v>419</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BM10" t="n">
         <v>419</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BN10" t="n">
         <v>419</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BO10" t="n">
         <v>419</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BP10" t="n">
         <v>419</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BQ10" t="n">
         <v>419</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BR10" t="n">
         <v>419</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BS10" t="n">
         <v>419</v>
       </c>
-      <c r="BK10" t="n">
+      <c r="BT10" t="n">
         <v>633</v>
       </c>
-      <c r="BL10" t="n">
+      <c r="BU10" t="n">
         <v>633</v>
       </c>
-      <c r="BM10" t="n">
+      <c r="BV10" t="n">
         <v>633</v>
       </c>
-      <c r="BN10" t="n">
+      <c r="BW10" t="n">
         <v>633</v>
       </c>
-      <c r="BO10" t="n">
+      <c r="BX10" t="n">
         <v>633</v>
       </c>
-      <c r="BP10" t="n">
+      <c r="BY10" t="n">
         <v>633</v>
       </c>
-      <c r="BQ10" t="n">
+      <c r="BZ10" t="n">
         <v>633</v>
       </c>
-      <c r="BR10" t="n">
+      <c r="CA10" t="n">
         <v>633</v>
       </c>
-      <c r="BS10" t="n">
+      <c r="CB10" t="n">
         <v>633</v>
       </c>
-      <c r="BT10" t="n">
+      <c r="CC10" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BU10" t="n">
+      <c r="CD10" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BV10" t="n">
+      <c r="CE10" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BW10" t="n">
+      <c r="CF10" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="CG10" t="n">
         <v>0.8</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="CH10" t="n">
         <v>0.7916666666666666</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="CI10" t="n">
         <v>0</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CJ10" t="n">
         <v>0.75</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CK10" t="n">
         <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>493.4</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>45.23</v>
       </c>
     </row>
     <row r="11">
@@ -3054,10 +3406,10 @@
         <v>499</v>
       </c>
       <c r="C11" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D11" t="n">
         <v>38</v>
-      </c>
-      <c r="D11" t="n">
-        <v>56.33802816901409</v>
       </c>
       <c r="E11" t="n">
         <v>499</v>
@@ -3066,228 +3418,261 @@
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>74.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>499.3783522382377</v>
-      </c>
-      <c r="J11" t="n">
-        <v>40.02117422362872</v>
-      </c>
-      <c r="K11" t="n">
-        <v>500.8720417010023</v>
-      </c>
-      <c r="L11" t="n">
-        <v>37.06653886935749</v>
-      </c>
-      <c r="M11" t="n">
-        <v>499.7346970491785</v>
-      </c>
-      <c r="N11" t="n">
-        <v>36.12750151886689</v>
-      </c>
-      <c r="O11" t="n">
-        <v>499.6128610451709</v>
-      </c>
-      <c r="P11" t="n">
-        <v>35.35311967053935</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>496.9704165490081</v>
-      </c>
       <c r="R11" t="n">
-        <v>37.47539907161469</v>
+        <v>499.38</v>
       </c>
       <c r="S11" t="n">
-        <v>499.3496178105153</v>
+        <v>40.02</v>
       </c>
       <c r="T11" t="n">
-        <v>39.22556081836044</v>
+        <v>500.87</v>
       </c>
       <c r="U11" t="n">
-        <v>499.8209744123255</v>
+        <v>37.07</v>
       </c>
       <c r="V11" t="n">
-        <v>38.74883414319439</v>
+        <v>499.73</v>
       </c>
       <c r="W11" t="n">
-        <v>502.834341976721</v>
+        <v>36.13</v>
       </c>
       <c r="X11" t="n">
-        <v>42.97244559530715</v>
+        <v>499.61</v>
       </c>
       <c r="Y11" t="n">
-        <v>499.1177441826127</v>
+        <v>35.35</v>
       </c>
       <c r="Z11" t="n">
-        <v>44.80954820782995</v>
+        <v>496.97</v>
       </c>
       <c r="AA11" t="n">
+        <v>37.48</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>499.35</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>39.23</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>499.82</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>502.83</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>42.97</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>499.12</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>44.81</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>-0.15</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AK11" t="n">
         <v>-0.1525423728813559</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AL11" t="n">
         <v>-0.1392405063291139</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AM11" t="n">
         <v>-0.1111111111111111</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AN11" t="n">
         <v>-0.09243697478991597</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AO11" t="n">
         <v>-0.06474820143884892</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AP11" t="n">
         <v>-0.06918238993710692</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AQ11" t="n">
         <v>-0.02793296089385475</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AR11" t="n">
         <v>-0.05527638190954774</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AS11" t="n">
         <v>495.325</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AT11" t="n">
         <v>498.45</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AU11" t="n">
         <v>498.375</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AV11" t="n">
         <v>498.49</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AW11" t="n">
         <v>498.8</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AX11" t="n">
         <v>499.5142857142857</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AY11" t="n">
         <v>499.05</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AZ11" t="n">
         <v>500.7388888888889</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="BA11" t="n">
         <v>499.305</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="BB11" t="n">
         <v>54.86090935265291</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="BC11" t="n">
         <v>49.74616400621593</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="BD11" t="n">
         <v>46.55598108728888</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="BE11" t="n">
         <v>44.7998872766439</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="BF11" t="n">
         <v>43.46293440009161</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="BG11" t="n">
         <v>42.35740544365729</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="BH11" t="n">
         <v>42.36018177486966</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BI11" t="n">
         <v>42.13040125463492</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BJ11" t="n">
         <v>42.71067752916125</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BK11" t="n">
         <v>379</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BL11" t="n">
         <v>379</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BM11" t="n">
         <v>379</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BN11" t="n">
         <v>379</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="BO11" t="n">
         <v>379</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BP11" t="n">
         <v>379</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BQ11" t="n">
         <v>379</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BR11" t="n">
         <v>379</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BS11" t="n">
         <v>379</v>
       </c>
-      <c r="BK11" t="n">
+      <c r="BT11" t="n">
         <v>635</v>
       </c>
-      <c r="BL11" t="n">
+      <c r="BU11" t="n">
         <v>635</v>
       </c>
-      <c r="BM11" t="n">
+      <c r="BV11" t="n">
         <v>635</v>
       </c>
-      <c r="BN11" t="n">
+      <c r="BW11" t="n">
         <v>635</v>
       </c>
-      <c r="BO11" t="n">
+      <c r="BX11" t="n">
         <v>635</v>
       </c>
-      <c r="BP11" t="n">
+      <c r="BY11" t="n">
         <v>635</v>
       </c>
-      <c r="BQ11" t="n">
+      <c r="BZ11" t="n">
         <v>635</v>
       </c>
-      <c r="BR11" t="n">
+      <c r="CA11" t="n">
         <v>635</v>
       </c>
-      <c r="BS11" t="n">
+      <c r="CB11" t="n">
         <v>635</v>
       </c>
-      <c r="BT11" t="n">
+      <c r="CC11" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU11" t="n">
+      <c r="CD11" t="n">
         <v>0.75</v>
       </c>
-      <c r="BV11" t="n">
+      <c r="CE11" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BW11" t="n">
+      <c r="CF11" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="BX11" t="n">
+      <c r="CG11" t="n">
         <v>0.9130434782608695</v>
       </c>
-      <c r="BY11" t="n">
+      <c r="CH11" t="n">
         <v>0.9642857142857143</v>
       </c>
-      <c r="BZ11" t="n">
+      <c r="CI11" t="n">
         <v>0.9393939393939394</v>
       </c>
-      <c r="CA11" t="n">
+      <c r="CJ11" t="n">
         <v>0.9722222222222222</v>
       </c>
-      <c r="CB11" t="n">
+      <c r="CK11" t="n">
         <v>0.9285714285714286</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>499.12</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>44.81</v>
       </c>
     </row>
     <row r="12">
@@ -3300,10 +3685,10 @@
         <v>502</v>
       </c>
       <c r="C12" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D12" t="n">
         <v>38</v>
-      </c>
-      <c r="D12" t="n">
-        <v>56.33802816901409</v>
       </c>
       <c r="E12" t="n">
         <v>502</v>
@@ -3312,228 +3697,261 @@
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>503.1734501045852</v>
-      </c>
-      <c r="J12" t="n">
-        <v>61.78430819736373</v>
-      </c>
-      <c r="K12" t="n">
-        <v>499.2991499150544</v>
-      </c>
-      <c r="L12" t="n">
-        <v>58.9078113367151</v>
-      </c>
-      <c r="M12" t="n">
-        <v>502.8384789644176</v>
-      </c>
-      <c r="N12" t="n">
-        <v>52.92763558938054</v>
-      </c>
-      <c r="O12" t="n">
-        <v>497.0947958138734</v>
-      </c>
-      <c r="P12" t="n">
-        <v>49.65189609831519</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>495.6916169928421</v>
-      </c>
       <c r="R12" t="n">
-        <v>50.04078799003201</v>
+        <v>503.17</v>
       </c>
       <c r="S12" t="n">
-        <v>495.9465581263775</v>
+        <v>61.78</v>
       </c>
       <c r="T12" t="n">
-        <v>49.97523570554691</v>
+        <v>499.3</v>
       </c>
       <c r="U12" t="n">
-        <v>491.9599077269152</v>
+        <v>58.91</v>
       </c>
       <c r="V12" t="n">
-        <v>49.01305573308358</v>
+        <v>502.84</v>
       </c>
       <c r="W12" t="n">
-        <v>494.4015172584448</v>
+        <v>52.93</v>
       </c>
       <c r="X12" t="n">
-        <v>45.54233220077567</v>
+        <v>497.09</v>
       </c>
       <c r="Y12" t="n">
-        <v>497.0423230950138</v>
+        <v>49.65</v>
       </c>
       <c r="Z12" t="n">
-        <v>44.80491288754961</v>
+        <v>495.69</v>
       </c>
       <c r="AA12" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>495.95</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>49.98</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>491.96</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>49.01</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>494.4</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>497.04</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AK12" t="n">
         <v>-0.03333333333333333</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AL12" t="n">
         <v>-0.025</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AM12" t="n">
         <v>0</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AN12" t="n">
         <v>0</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AO12" t="n">
         <v>0.01428571428571429</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AP12" t="n">
         <v>0.025</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AQ12" t="n">
         <v>0.02222222222222222</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AR12" t="n">
         <v>0.01</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AS12" t="n">
         <v>496</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AT12" t="n">
         <v>498.25</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AU12" t="n">
         <v>498.8125</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AV12" t="n">
         <v>500.64</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AW12" t="n">
         <v>498.875</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AX12" t="n">
         <v>498.5</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AY12" t="n">
         <v>498.23125</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AZ12" t="n">
         <v>497.3944444444444</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="BA12" t="n">
         <v>496.685</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="BB12" t="n">
         <v>62.75946143809713</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="BC12" t="n">
         <v>62.80329741873962</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BD12" t="n">
         <v>61.65510801020464</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="BE12" t="n">
         <v>58.19785563059862</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="BF12" t="n">
         <v>55.80689361539486</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="BG12" t="n">
         <v>54.25080644561886</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="BH12" t="n">
         <v>53.37113239793118</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BI12" t="n">
         <v>52.17444001959221</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BJ12" t="n">
         <v>51.07000856667248</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BK12" t="n">
         <v>348</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BL12" t="n">
         <v>348</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BM12" t="n">
         <v>348</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BN12" t="n">
         <v>348</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BO12" t="n">
         <v>348</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BP12" t="n">
         <v>348</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BQ12" t="n">
         <v>348</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BR12" t="n">
         <v>348</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BS12" t="n">
         <v>348</v>
       </c>
-      <c r="BK12" t="n">
+      <c r="BT12" t="n">
         <v>591</v>
       </c>
-      <c r="BL12" t="n">
+      <c r="BU12" t="n">
         <v>591</v>
       </c>
-      <c r="BM12" t="n">
+      <c r="BV12" t="n">
         <v>591</v>
       </c>
-      <c r="BN12" t="n">
+      <c r="BW12" t="n">
         <v>591</v>
       </c>
-      <c r="BO12" t="n">
+      <c r="BX12" t="n">
         <v>591</v>
       </c>
-      <c r="BP12" t="n">
+      <c r="BY12" t="n">
         <v>591</v>
       </c>
-      <c r="BQ12" t="n">
+      <c r="BZ12" t="n">
         <v>591</v>
       </c>
-      <c r="BR12" t="n">
+      <c r="CA12" t="n">
         <v>591</v>
       </c>
-      <c r="BS12" t="n">
+      <c r="CB12" t="n">
         <v>591</v>
       </c>
-      <c r="BT12" t="n">
+      <c r="CC12" t="n">
         <v>1</v>
       </c>
-      <c r="BU12" t="n">
+      <c r="CD12" t="n">
         <v>1</v>
       </c>
-      <c r="BV12" t="n">
+      <c r="CE12" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="BW12" t="n">
+      <c r="CF12" t="n">
         <v>1</v>
       </c>
-      <c r="BX12" t="n">
+      <c r="CG12" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BY12" t="n">
+      <c r="CH12" t="n">
         <v>0.8636363636363636</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="CI12" t="n">
         <v>0.04347826086956522</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="CJ12" t="n">
         <v>0.8</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CK12" t="n">
         <v>0.7837837837837838</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>497.04</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>44.8</v>
       </c>
     </row>
     <row r="13">
@@ -3546,10 +3964,10 @@
         <v>499</v>
       </c>
       <c r="C13" t="n">
+        <v>60.78576723498888</v>
+      </c>
+      <c r="D13" t="n">
         <v>41</v>
-      </c>
-      <c r="D13" t="n">
-        <v>60.78576723498888</v>
       </c>
       <c r="E13" t="n">
         <v>499</v>
@@ -3558,228 +3976,261 @@
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>73.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>528.6992104955336</v>
-      </c>
-      <c r="J13" t="n">
-        <v>27.52300505669567</v>
-      </c>
-      <c r="K13" t="n">
-        <v>521.6226479373507</v>
-      </c>
-      <c r="L13" t="n">
-        <v>28.00362889922254</v>
-      </c>
-      <c r="M13" t="n">
-        <v>520.9702727507404</v>
-      </c>
-      <c r="N13" t="n">
-        <v>34.83879470253409</v>
-      </c>
-      <c r="O13" t="n">
-        <v>515.6768630853261</v>
-      </c>
-      <c r="P13" t="n">
-        <v>36.85854527015154</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>509.6544277089121</v>
-      </c>
       <c r="R13" t="n">
-        <v>42.31975785982584</v>
+        <v>528.7</v>
       </c>
       <c r="S13" t="n">
-        <v>505.2321443975598</v>
+        <v>27.52</v>
       </c>
       <c r="T13" t="n">
-        <v>53.76470663082851</v>
+        <v>521.62</v>
       </c>
       <c r="U13" t="n">
-        <v>504.3367279868348</v>
+        <v>28</v>
       </c>
       <c r="V13" t="n">
-        <v>60.45738967694788</v>
+        <v>520.97</v>
       </c>
       <c r="W13" t="n">
-        <v>502.8348087850547</v>
+        <v>34.84</v>
       </c>
       <c r="X13" t="n">
-        <v>57.32225454569632</v>
+        <v>515.6799999999999</v>
       </c>
       <c r="Y13" t="n">
-        <v>502.8577315648599</v>
+        <v>36.86</v>
       </c>
       <c r="Z13" t="n">
-        <v>58.50011327839851</v>
+        <v>509.65</v>
       </c>
       <c r="AA13" t="n">
+        <v>42.32</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>505.23</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>53.76</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>504.34</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>60.46</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>502.83</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>57.32</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>502.86</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>0.5384615384615384</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AK13" t="n">
         <v>0.3559322033898305</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AL13" t="n">
         <v>0.3766233766233766</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AM13" t="n">
         <v>0.1958762886597938</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AN13" t="n">
         <v>0.05982905982905983</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AO13" t="n">
         <v>-0.0364963503649635</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AP13" t="n">
         <v>-0.04458598726114649</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AQ13" t="n">
         <v>-0.07344632768361582</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AR13" t="n">
         <v>-0.06598984771573604</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AS13" t="n">
         <v>529.45</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AT13" t="n">
         <v>525.0666666666667</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AU13" t="n">
         <v>525.325</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AV13" t="n">
         <v>519.8</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AW13" t="n">
         <v>513.6416666666667</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AX13" t="n">
         <v>507.5285714285714</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AY13" t="n">
         <v>506.35</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AZ13" t="n">
         <v>503.5277777777778</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="BA13" t="n">
         <v>503.485</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="BB13" t="n">
         <v>33.46188129797844</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="BC13" t="n">
         <v>35.36376048379974</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="BD13" t="n">
         <v>34.80652776419964</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="BE13" t="n">
         <v>36.76084873884171</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="BF13" t="n">
         <v>39.57035839980337</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="BG13" t="n">
         <v>43.80581221337494</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="BH13" t="n">
         <v>48.04128432921002</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BI13" t="n">
         <v>51.6463864021004</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BJ13" t="n">
         <v>53.60624753701754</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BK13" t="n">
         <v>463</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BL13" t="n">
         <v>463</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BM13" t="n">
         <v>463</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BN13" t="n">
         <v>458</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BO13" t="n">
         <v>446</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BP13" t="n">
         <v>432</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BQ13" t="n">
         <v>421</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BR13" t="n">
         <v>409</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BS13" t="n">
         <v>409</v>
       </c>
-      <c r="BK13" t="n">
+      <c r="BT13" t="n">
         <v>634</v>
       </c>
-      <c r="BL13" t="n">
+      <c r="BU13" t="n">
         <v>634</v>
       </c>
-      <c r="BM13" t="n">
+      <c r="BV13" t="n">
         <v>634</v>
       </c>
-      <c r="BN13" t="n">
+      <c r="BW13" t="n">
         <v>634</v>
       </c>
-      <c r="BO13" t="n">
+      <c r="BX13" t="n">
         <v>634</v>
       </c>
-      <c r="BP13" t="n">
+      <c r="BY13" t="n">
         <v>634</v>
       </c>
-      <c r="BQ13" t="n">
+      <c r="BZ13" t="n">
         <v>634</v>
       </c>
-      <c r="BR13" t="n">
+      <c r="CA13" t="n">
         <v>634</v>
       </c>
-      <c r="BS13" t="n">
+      <c r="CB13" t="n">
         <v>634</v>
       </c>
-      <c r="BT13" t="n">
+      <c r="CC13" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BU13" t="n">
+      <c r="CD13" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BV13" t="n">
+      <c r="CE13" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BW13" t="n">
+      <c r="CF13" t="n">
         <v>0.8125</v>
       </c>
-      <c r="BX13" t="n">
+      <c r="CG13" t="n">
         <v>0.7368421052631579</v>
       </c>
-      <c r="BY13" t="n">
+      <c r="CH13" t="n">
         <v>0.8947368421052632</v>
       </c>
-      <c r="BZ13" t="n">
+      <c r="CI13" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="CA13" t="n">
+      <c r="CJ13" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="CB13" t="n">
+      <c r="CK13" t="n">
         <v>0.7333333333333333</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>502.86</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>58.5</v>
       </c>
     </row>
     <row r="14">
@@ -3792,10 +4243,10 @@
         <v>502</v>
       </c>
       <c r="C14" t="n">
+        <v>59.30318754633062</v>
+      </c>
+      <c r="D14" t="n">
         <v>40</v>
-      </c>
-      <c r="D14" t="n">
-        <v>59.30318754633062</v>
       </c>
       <c r="E14" t="n">
         <v>502</v>
@@ -3804,228 +4255,261 @@
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>498.6199979328936</v>
-      </c>
-      <c r="J14" t="n">
-        <v>11.99900489285113</v>
-      </c>
-      <c r="K14" t="n">
-        <v>496.1440085806936</v>
-      </c>
-      <c r="L14" t="n">
-        <v>25.83907379660673</v>
-      </c>
-      <c r="M14" t="n">
-        <v>496.4724173365045</v>
-      </c>
-      <c r="N14" t="n">
-        <v>29.10401708163891</v>
-      </c>
-      <c r="O14" t="n">
-        <v>493.4647219519308</v>
-      </c>
-      <c r="P14" t="n">
-        <v>32.94169666339378</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>494.2959814578587</v>
-      </c>
       <c r="R14" t="n">
-        <v>32.85479472201743</v>
+        <v>498.62</v>
       </c>
       <c r="S14" t="n">
-        <v>490.8438764010946</v>
+        <v>12</v>
       </c>
       <c r="T14" t="n">
-        <v>34.81943772852503</v>
+        <v>496.14</v>
       </c>
       <c r="U14" t="n">
-        <v>490.1382466465758</v>
+        <v>25.84</v>
       </c>
       <c r="V14" t="n">
-        <v>33.39578885578673</v>
+        <v>496.47</v>
       </c>
       <c r="W14" t="n">
-        <v>489.8800316795521</v>
+        <v>29.1</v>
       </c>
       <c r="X14" t="n">
-        <v>33.18030655547692</v>
+        <v>493.46</v>
       </c>
       <c r="Y14" t="n">
-        <v>492.1382588213237</v>
+        <v>32.94</v>
       </c>
       <c r="Z14" t="n">
-        <v>35.73053217459761</v>
+        <v>494.3</v>
       </c>
       <c r="AA14" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>490.84</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>34.82</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>490.14</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>489.88</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>33.18</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>492.14</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>35.73</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AK14" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AL14" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AM14" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AN14" t="n">
         <v>-0.08333333333333333</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AO14" t="n">
         <v>-0.1285714285714286</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AP14" t="n">
         <v>-0.125</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AQ14" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AR14" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AS14" t="n">
         <v>503.225</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AT14" t="n">
         <v>499.6166666666667</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AU14" t="n">
         <v>497.65</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AV14" t="n">
         <v>495.96</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AW14" t="n">
         <v>496.2833333333334</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AX14" t="n">
         <v>492.8642857142857</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AY14" t="n">
         <v>492.06875</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AZ14" t="n">
         <v>492.3333333333333</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="BA14" t="n">
         <v>492.71</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="BB14" t="n">
         <v>28.80146480649899</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="BC14" t="n">
         <v>30.06109981724259</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="BD14" t="n">
         <v>33.13838408854602</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="BE14" t="n">
         <v>34.50504890592101</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="BF14" t="n">
         <v>36.24619137080321</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="BG14" t="n">
         <v>37.60665038342586</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="BH14" t="n">
         <v>37.29043474454944</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="BI14" t="n">
         <v>37.29179236477885</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BJ14" t="n">
         <v>37.17117028020506</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BK14" t="n">
         <v>455</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BL14" t="n">
         <v>450</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BM14" t="n">
         <v>444</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BN14" t="n">
         <v>444</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BO14" t="n">
         <v>439</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BP14" t="n">
         <v>433</v>
       </c>
-      <c r="BH14" t="n">
+      <c r="BQ14" t="n">
         <v>433</v>
       </c>
-      <c r="BI14" t="n">
+      <c r="BR14" t="n">
         <v>433</v>
       </c>
-      <c r="BJ14" t="n">
+      <c r="BS14" t="n">
         <v>433</v>
       </c>
-      <c r="BK14" t="n">
+      <c r="BT14" t="n">
         <v>643</v>
       </c>
-      <c r="BL14" t="n">
+      <c r="BU14" t="n">
         <v>643</v>
       </c>
-      <c r="BM14" t="n">
+      <c r="BV14" t="n">
         <v>643</v>
       </c>
-      <c r="BN14" t="n">
+      <c r="BW14" t="n">
         <v>643</v>
       </c>
-      <c r="BO14" t="n">
+      <c r="BX14" t="n">
         <v>643</v>
       </c>
-      <c r="BP14" t="n">
+      <c r="BY14" t="n">
         <v>643</v>
       </c>
-      <c r="BQ14" t="n">
+      <c r="BZ14" t="n">
         <v>643</v>
       </c>
-      <c r="BR14" t="n">
+      <c r="CA14" t="n">
         <v>643</v>
       </c>
-      <c r="BS14" t="n">
+      <c r="CB14" t="n">
         <v>643</v>
       </c>
-      <c r="BT14" t="n">
+      <c r="CC14" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BU14" t="n">
+      <c r="CD14" t="n">
         <v>0.6153846153846154</v>
       </c>
-      <c r="BV14" t="n">
+      <c r="CE14" t="n">
         <v>0.5625</v>
       </c>
-      <c r="BW14" t="n">
+      <c r="CF14" t="n">
         <v>0.6875</v>
       </c>
-      <c r="BX14" t="n">
+      <c r="CG14" t="n">
         <v>0.7368421052631579</v>
       </c>
-      <c r="BY14" t="n">
+      <c r="CH14" t="n">
         <v>0.72</v>
       </c>
-      <c r="BZ14" t="n">
+      <c r="CI14" t="n">
         <v>0.7241379310344828</v>
       </c>
-      <c r="CA14" t="n">
+      <c r="CJ14" t="n">
         <v>0.7941176470588235</v>
       </c>
-      <c r="CB14" t="n">
+      <c r="CK14" t="n">
         <v>0.8888888888888888</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>492.14</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>35.73</v>
       </c>
     </row>
     <row r="15">
@@ -4038,10 +4522,10 @@
         <v>498</v>
       </c>
       <c r="C15" t="n">
+        <v>57.82060785767235</v>
+      </c>
+      <c r="D15" t="n">
         <v>39</v>
-      </c>
-      <c r="D15" t="n">
-        <v>57.82060785767235</v>
       </c>
       <c r="E15" t="n">
         <v>498</v>
@@ -4050,228 +4534,261 @@
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>74.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>492.436951945345</v>
-      </c>
-      <c r="J15" t="n">
-        <v>36.2082407305547</v>
-      </c>
-      <c r="K15" t="n">
-        <v>494.7608253559343</v>
-      </c>
-      <c r="L15" t="n">
-        <v>37.51318428164934</v>
-      </c>
-      <c r="M15" t="n">
-        <v>489.9309312382708</v>
-      </c>
-      <c r="N15" t="n">
-        <v>35.66507311462205</v>
-      </c>
-      <c r="O15" t="n">
-        <v>497.0142854172667</v>
-      </c>
-      <c r="P15" t="n">
-        <v>40.79434806353748</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>499.8886181428869</v>
-      </c>
       <c r="R15" t="n">
-        <v>40.27971767437404</v>
+        <v>492.44</v>
       </c>
       <c r="S15" t="n">
-        <v>500.9987697927856</v>
+        <v>36.21</v>
       </c>
       <c r="T15" t="n">
-        <v>37.30883613817891</v>
+        <v>494.76</v>
       </c>
       <c r="U15" t="n">
-        <v>500.0749930959068</v>
+        <v>37.51</v>
       </c>
       <c r="V15" t="n">
-        <v>42.94303007937862</v>
+        <v>489.93</v>
       </c>
       <c r="W15" t="n">
-        <v>500.4440598884186</v>
+        <v>35.67</v>
       </c>
       <c r="X15" t="n">
-        <v>42.88355322286836</v>
+        <v>497.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>502.5875578784472</v>
+        <v>40.79</v>
       </c>
       <c r="Z15" t="n">
-        <v>44.40623989364103</v>
+        <v>499.89</v>
       </c>
       <c r="AA15" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>501</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>37.31</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>500.07</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>42.94</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>500.44</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>42.88</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>502.59</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>44.41</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>-0.2307692307692308</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AK15" t="n">
         <v>-0.05084745762711865</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AL15" t="n">
         <v>-0.0379746835443038</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AM15" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AN15" t="n">
         <v>0.02521008403361345</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AO15" t="n">
         <v>0.02158273381294964</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AP15" t="n">
         <v>0.01886792452830189</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AQ15" t="n">
         <v>0.01675977653631285</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AR15" t="n">
         <v>0.03517587939698492</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AS15" t="n">
         <v>496.025</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AT15" t="n">
         <v>498.95</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AU15" t="n">
         <v>495.0875</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AV15" t="n">
         <v>495.86</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AW15" t="n">
         <v>497.35</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AX15" t="n">
         <v>497.5857142857143</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AY15" t="n">
         <v>498.225</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AZ15" t="n">
         <v>498.8666666666667</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="BA15" t="n">
         <v>500.085</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="BB15" t="n">
         <v>43.74213500733589</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="BC15" t="n">
         <v>43.25445063805573</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="BD15" t="n">
         <v>42.41173002543047</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="BE15" t="n">
         <v>42.1789094216529</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="BF15" t="n">
         <v>42.19827208152802</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="BG15" t="n">
         <v>41.20401951860759</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="BH15" t="n">
         <v>40.8313528431278</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="BI15" t="n">
         <v>41.53504544357692</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BJ15" t="n">
         <v>41.90570098447226</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BK15" t="n">
         <v>364</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BL15" t="n">
         <v>364</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BM15" t="n">
         <v>364</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BN15" t="n">
         <v>364</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BO15" t="n">
         <v>364</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BP15" t="n">
         <v>364</v>
       </c>
-      <c r="BH15" t="n">
+      <c r="BQ15" t="n">
         <v>364</v>
       </c>
-      <c r="BI15" t="n">
+      <c r="BR15" t="n">
         <v>364</v>
       </c>
-      <c r="BJ15" t="n">
+      <c r="BS15" t="n">
         <v>364</v>
       </c>
-      <c r="BK15" t="n">
+      <c r="BT15" t="n">
         <v>563</v>
       </c>
-      <c r="BL15" t="n">
+      <c r="BU15" t="n">
         <v>563</v>
       </c>
-      <c r="BM15" t="n">
+      <c r="BV15" t="n">
         <v>563</v>
       </c>
-      <c r="BN15" t="n">
+      <c r="BW15" t="n">
         <v>563</v>
       </c>
-      <c r="BO15" t="n">
+      <c r="BX15" t="n">
         <v>563</v>
       </c>
-      <c r="BP15" t="n">
+      <c r="BY15" t="n">
         <v>563</v>
       </c>
-      <c r="BQ15" t="n">
+      <c r="BZ15" t="n">
         <v>563</v>
       </c>
-      <c r="BR15" t="n">
+      <c r="CA15" t="n">
         <v>563</v>
       </c>
-      <c r="BS15" t="n">
+      <c r="CB15" t="n">
         <v>563</v>
       </c>
-      <c r="BT15" t="n">
+      <c r="CC15" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BU15" t="n">
+      <c r="CD15" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BV15" t="n">
+      <c r="CE15" t="n">
         <v>0.9</v>
       </c>
-      <c r="BW15" t="n">
+      <c r="CF15" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="BX15" t="n">
+      <c r="CG15" t="n">
         <v>0.8</v>
       </c>
-      <c r="BY15" t="n">
+      <c r="CH15" t="n">
         <v>0</v>
       </c>
-      <c r="BZ15" t="n">
+      <c r="CI15" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="CA15" t="n">
+      <c r="CJ15" t="n">
         <v>0.88</v>
       </c>
-      <c r="CB15" t="n">
+      <c r="CK15" t="n">
         <v>0.8064516129032258</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>502.59</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>44.41</v>
       </c>
     </row>
     <row r="16">
@@ -4284,10 +4801,10 @@
         <v>500</v>
       </c>
       <c r="C16" t="n">
+        <v>57.82060785767235</v>
+      </c>
+      <c r="D16" t="n">
         <v>39</v>
-      </c>
-      <c r="D16" t="n">
-        <v>57.82060785767235</v>
       </c>
       <c r="E16" t="n">
         <v>500</v>
@@ -4296,228 +4813,261 @@
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>490.9310315752427</v>
-      </c>
-      <c r="J16" t="n">
-        <v>53.61600383200517</v>
-      </c>
-      <c r="K16" t="n">
-        <v>497.6063651419971</v>
-      </c>
-      <c r="L16" t="n">
-        <v>66.06344666713113</v>
-      </c>
-      <c r="M16" t="n">
-        <v>501.1280665531528</v>
-      </c>
-      <c r="N16" t="n">
-        <v>56.35061230301027</v>
-      </c>
-      <c r="O16" t="n">
-        <v>502.7796497083096</v>
-      </c>
-      <c r="P16" t="n">
-        <v>53.02367798605099</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>506.6244172829019</v>
-      </c>
       <c r="R16" t="n">
-        <v>47.4887805763139</v>
+        <v>490.93</v>
       </c>
       <c r="S16" t="n">
-        <v>503.6353747480191</v>
+        <v>53.62</v>
       </c>
       <c r="T16" t="n">
-        <v>45.89113722975463</v>
+        <v>497.61</v>
       </c>
       <c r="U16" t="n">
-        <v>503.8190480492903</v>
+        <v>66.06</v>
       </c>
       <c r="V16" t="n">
-        <v>45.84470684413091</v>
+        <v>501.13</v>
       </c>
       <c r="W16" t="n">
-        <v>501.5397384013005</v>
+        <v>56.35</v>
       </c>
       <c r="X16" t="n">
-        <v>46.38655175417518</v>
+        <v>502.78</v>
       </c>
       <c r="Y16" t="n">
-        <v>501.8981200974493</v>
+        <v>53.02</v>
       </c>
       <c r="Z16" t="n">
-        <v>44.93296160435284</v>
+        <v>506.62</v>
       </c>
       <c r="AA16" t="n">
+        <v>47.49</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>503.64</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>45.89</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>503.82</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>45.84</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>501.54</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>46.39</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>501.9</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>44.93</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>-0.4358974358974359</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AK16" t="n">
         <v>-0.1525423728813559</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AL16" t="n">
         <v>-0.0379746835443038</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AM16" t="n">
         <v>-0.0101010101010101</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AN16" t="n">
         <v>0.008403361344537815</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AO16" t="n">
         <v>0.03597122302158273</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AP16" t="n">
         <v>0.0440251572327044</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AQ16" t="n">
         <v>0.02793296089385475</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AR16" t="n">
         <v>0.03517587939698492</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AS16" t="n">
         <v>485.475</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AT16" t="n">
         <v>497.0333333333334</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AU16" t="n">
         <v>502.9375</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AV16" t="n">
         <v>503.82</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AW16" t="n">
         <v>505.05</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AX16" t="n">
         <v>505.1071428571428</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AY16" t="n">
         <v>504.975</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AZ16" t="n">
         <v>503.9888888888889</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="BA16" t="n">
         <v>503.905</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="BB16" t="n">
         <v>38.59468065679518</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="BC16" t="n">
         <v>52.85103804299612</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="BD16" t="n">
         <v>59.4515230566047</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="BE16" t="n">
         <v>59.35610836299832</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="BF16" t="n">
         <v>57.48533871055007</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="BG16" t="n">
         <v>55.38020487355328</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="BH16" t="n">
         <v>53.66003517516551</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BI16" t="n">
         <v>52.83401565162868</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BJ16" t="n">
         <v>51.92808464597939</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BK16" t="n">
         <v>339</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BL16" t="n">
         <v>339</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BM16" t="n">
         <v>339</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BN16" t="n">
         <v>339</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BO16" t="n">
         <v>339</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BP16" t="n">
         <v>339</v>
       </c>
-      <c r="BH16" t="n">
+      <c r="BQ16" t="n">
         <v>339</v>
       </c>
-      <c r="BI16" t="n">
+      <c r="BR16" t="n">
         <v>339</v>
       </c>
-      <c r="BJ16" t="n">
+      <c r="BS16" t="n">
         <v>339</v>
       </c>
-      <c r="BK16" t="n">
+      <c r="BT16" t="n">
         <v>557</v>
       </c>
-      <c r="BL16" t="n">
+      <c r="BU16" t="n">
         <v>589</v>
       </c>
-      <c r="BM16" t="n">
+      <c r="BV16" t="n">
         <v>595</v>
       </c>
-      <c r="BN16" t="n">
+      <c r="BW16" t="n">
         <v>595</v>
       </c>
-      <c r="BO16" t="n">
+      <c r="BX16" t="n">
         <v>595</v>
       </c>
-      <c r="BP16" t="n">
+      <c r="BY16" t="n">
         <v>595</v>
       </c>
-      <c r="BQ16" t="n">
+      <c r="BZ16" t="n">
         <v>595</v>
       </c>
-      <c r="BR16" t="n">
+      <c r="CA16" t="n">
         <v>595</v>
       </c>
-      <c r="BS16" t="n">
+      <c r="CB16" t="n">
         <v>595</v>
       </c>
-      <c r="BT16" t="n">
+      <c r="CC16" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="BU16" t="n">
+      <c r="CD16" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="BV16" t="n">
+      <c r="CE16" t="n">
         <v>0.7</v>
       </c>
-      <c r="BW16" t="n">
+      <c r="CF16" t="n">
         <v>0.625</v>
       </c>
-      <c r="BX16" t="n">
+      <c r="CG16" t="n">
         <v>0.85</v>
       </c>
-      <c r="BY16" t="n">
+      <c r="CH16" t="n">
         <v>0.95</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="CI16" t="n">
         <v>0.9130434782608695</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CJ16" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="CB16" t="n">
+      <c r="CK16" t="n">
         <v>0.9375</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>501.9</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>44.93</v>
       </c>
     </row>
     <row r="17">
@@ -4530,10 +5080,10 @@
         <v>499</v>
       </c>
       <c r="C17" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>56.33802816901409</v>
       </c>
       <c r="E17" t="n">
         <v>499</v>
@@ -4542,720 +5092,819 @@
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>75.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>484.6277773351564</v>
-      </c>
-      <c r="J17" t="n">
-        <v>19.53774199768766</v>
-      </c>
-      <c r="K17" t="n">
-        <v>488.0469481487164</v>
-      </c>
-      <c r="L17" t="n">
-        <v>37.842951232412</v>
-      </c>
-      <c r="M17" t="n">
-        <v>494.8358975679059</v>
-      </c>
-      <c r="N17" t="n">
-        <v>44.56397858090009</v>
-      </c>
-      <c r="O17" t="n">
-        <v>496.4339360951489</v>
-      </c>
-      <c r="P17" t="n">
-        <v>38.03054593840529</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>496.8290648675007</v>
-      </c>
       <c r="R17" t="n">
-        <v>37.20877509486783</v>
+        <v>484.63</v>
       </c>
       <c r="S17" t="n">
-        <v>500.9528651853018</v>
+        <v>19.54</v>
       </c>
       <c r="T17" t="n">
-        <v>38.13184251694421</v>
+        <v>488.05</v>
       </c>
       <c r="U17" t="n">
-        <v>503.9570822396213</v>
+        <v>37.84</v>
       </c>
       <c r="V17" t="n">
-        <v>45.34956371265341</v>
+        <v>494.84</v>
       </c>
       <c r="W17" t="n">
-        <v>502.3941971801152</v>
+        <v>44.56</v>
       </c>
       <c r="X17" t="n">
-        <v>42.88576293202994</v>
+        <v>496.43</v>
       </c>
       <c r="Y17" t="n">
-        <v>500.1375817897763</v>
+        <v>38.03</v>
       </c>
       <c r="Z17" t="n">
-        <v>41.66480724571781</v>
+        <v>496.83</v>
       </c>
       <c r="AA17" t="n">
+        <v>37.21</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>500.95</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>38.13</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>503.96</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>45.35</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>502.39</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>42.89</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>500.14</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>41.66</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>-0.4736842105263158</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AK17" t="n">
         <v>-0.2413793103448276</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AL17" t="n">
         <v>-0.05128205128205128</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AM17" t="n">
         <v>0</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AN17" t="n">
         <v>0.01694915254237288</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AO17" t="n">
         <v>0.02898550724637681</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AP17" t="n">
         <v>0.0759493670886076</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AQ17" t="n">
         <v>0.05617977528089887</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AR17" t="n">
         <v>0.0303030303030303</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AS17" t="n">
         <v>482</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AT17" t="n">
         <v>487.0166666666667</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AU17" t="n">
         <v>493.7125</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AV17" t="n">
         <v>494.82</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AW17" t="n">
         <v>495.175</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AX17" t="n">
         <v>495.8214285714286</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AY17" t="n">
         <v>499.125</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AZ17" t="n">
         <v>499.2055555555556</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="BA17" t="n">
         <v>498.395</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="BB17" t="n">
         <v>31.30734738044729</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="BC17" t="n">
         <v>36.52875199376817</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="BD17" t="n">
         <v>40.89963134002554</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="BE17" t="n">
         <v>42.7243209425264</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="BF17" t="n">
         <v>42.89923513304171</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="BG17" t="n">
         <v>41.58489902032482</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="BH17" t="n">
         <v>42.42975813034997</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="BI17" t="n">
         <v>43.59302916015386</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BJ17" t="n">
         <v>43.70307740880498</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BK17" t="n">
         <v>352</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BL17" t="n">
         <v>352</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BM17" t="n">
         <v>352</v>
       </c>
-      <c r="BE17" t="n">
+      <c r="BN17" t="n">
         <v>352</v>
       </c>
-      <c r="BF17" t="n">
+      <c r="BO17" t="n">
         <v>352</v>
       </c>
-      <c r="BG17" t="n">
+      <c r="BP17" t="n">
         <v>352</v>
       </c>
-      <c r="BH17" t="n">
+      <c r="BQ17" t="n">
         <v>352</v>
       </c>
-      <c r="BI17" t="n">
+      <c r="BR17" t="n">
         <v>352</v>
       </c>
-      <c r="BJ17" t="n">
+      <c r="BS17" t="n">
         <v>352</v>
       </c>
-      <c r="BK17" t="n">
+      <c r="BT17" t="n">
         <v>537</v>
       </c>
-      <c r="BL17" t="n">
+      <c r="BU17" t="n">
         <v>550</v>
       </c>
-      <c r="BM17" t="n">
+      <c r="BV17" t="n">
         <v>569</v>
       </c>
-      <c r="BN17" t="n">
+      <c r="BW17" t="n">
         <v>569</v>
       </c>
-      <c r="BO17" t="n">
+      <c r="BX17" t="n">
         <v>569</v>
       </c>
-      <c r="BP17" t="n">
+      <c r="BY17" t="n">
         <v>569</v>
       </c>
-      <c r="BQ17" t="n">
+      <c r="BZ17" t="n">
         <v>569</v>
       </c>
-      <c r="BR17" t="n">
+      <c r="CA17" t="n">
         <v>569</v>
       </c>
-      <c r="BS17" t="n">
+      <c r="CB17" t="n">
         <v>569</v>
       </c>
-      <c r="BT17" t="n">
+      <c r="CC17" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BU17" t="n">
+      <c r="CD17" t="n">
         <v>0.9</v>
       </c>
-      <c r="BV17" t="n">
+      <c r="CE17" t="n">
         <v>0.9</v>
       </c>
-      <c r="BW17" t="n">
+      <c r="CF17" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="BX17" t="n">
+      <c r="CG17" t="n">
         <v>0.8235294117647058</v>
       </c>
-      <c r="BY17" t="n">
+      <c r="CH17" t="n">
         <v>0</v>
       </c>
-      <c r="BZ17" t="n">
+      <c r="CI17" t="n">
         <v>0.68</v>
       </c>
-      <c r="CA17" t="n">
+      <c r="CJ17" t="n">
         <v>0.84</v>
       </c>
-      <c r="CB17" t="n">
+      <c r="CK17" t="n">
         <v>0.9285714285714286</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>500.14</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>41.66</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S18_G5_500_42_ABS1</t>
+          <t>S17_G5_502_38_ABS1</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C18" t="n">
-        <v>42</v>
+        <v>56.33802816901409</v>
       </c>
       <c r="D18" t="n">
-        <v>62.26834692364714</v>
+        <v>38</v>
       </c>
       <c r="E18" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F18" t="n">
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>75</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>494.0102250455508</v>
-      </c>
-      <c r="J18" t="n">
-        <v>45.33689709762587</v>
-      </c>
-      <c r="K18" t="n">
-        <v>494.994140186397</v>
-      </c>
-      <c r="L18" t="n">
-        <v>48.13408951470489</v>
-      </c>
-      <c r="M18" t="n">
-        <v>492.5828435910976</v>
-      </c>
-      <c r="N18" t="n">
-        <v>49.36686613221106</v>
-      </c>
-      <c r="O18" t="n">
-        <v>499.6574323099995</v>
-      </c>
-      <c r="P18" t="n">
-        <v>45.11085887534016</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>498.1884680479493</v>
-      </c>
       <c r="R18" t="n">
-        <v>41.97506739887639</v>
+        <v>502.2</v>
       </c>
       <c r="S18" t="n">
-        <v>499.3936418020466</v>
+        <v>26.84</v>
       </c>
       <c r="T18" t="n">
-        <v>43.96987460349512</v>
+        <v>506.58</v>
       </c>
       <c r="U18" t="n">
-        <v>496.297152918828</v>
+        <v>38.31</v>
       </c>
       <c r="V18" t="n">
-        <v>45.43853178590162</v>
+        <v>508.91</v>
       </c>
       <c r="W18" t="n">
-        <v>496.7455475861294</v>
+        <v>33.31</v>
       </c>
       <c r="X18" t="n">
-        <v>47.56688728881561</v>
+        <v>513.52</v>
       </c>
       <c r="Y18" t="n">
-        <v>499.2674565033566</v>
+        <v>40.44</v>
       </c>
       <c r="Z18" t="n">
-        <v>51.81744413672297</v>
+        <v>515.23</v>
       </c>
       <c r="AA18" t="n">
+        <v>42.37</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>512.84</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>41.01</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>510.71</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>41.65</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>506.62</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>45.04</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>503.59</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>44.75</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AB18" t="n">
-        <v>-0.06666666666666667</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>-0.06666666666666667</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>-0.05714285714285714</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>-0.0375</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>-0.04444444444444445</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>492.975</v>
-      </c>
       <c r="AK18" t="n">
-        <v>490.9333333333333</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="AL18" t="n">
-        <v>492.3125</v>
+        <v>0.05</v>
       </c>
       <c r="AM18" t="n">
-        <v>493.06</v>
+        <v>0.08</v>
       </c>
       <c r="AN18" t="n">
-        <v>493.1916666666667</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="AO18" t="n">
-        <v>494.9</v>
+        <v>0.05714285714285714</v>
       </c>
       <c r="AP18" t="n">
-        <v>495.9875</v>
+        <v>0.0375</v>
       </c>
       <c r="AQ18" t="n">
-        <v>495.4833333333333</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>497.805</v>
+        <v>-0.02</v>
       </c>
       <c r="AS18" t="n">
-        <v>49.66814245570293</v>
+        <v>500.975</v>
       </c>
       <c r="AT18" t="n">
-        <v>53.36973757560448</v>
+        <v>507.4666666666666</v>
       </c>
       <c r="AU18" t="n">
-        <v>53.47770417426313</v>
+        <v>507.675</v>
       </c>
       <c r="AV18" t="n">
-        <v>52.42782085877688</v>
+        <v>510.29</v>
       </c>
       <c r="AW18" t="n">
-        <v>50.08081732448951</v>
+        <v>511.0166666666667</v>
       </c>
       <c r="AX18" t="n">
-        <v>48.80124412933986</v>
+        <v>511.8785714285714</v>
       </c>
       <c r="AY18" t="n">
-        <v>48.36075210074797</v>
+        <v>511.09375</v>
       </c>
       <c r="AZ18" t="n">
-        <v>47.86804489659278</v>
+        <v>509.3777777777778</v>
       </c>
       <c r="BA18" t="n">
-        <v>48.52573518247817</v>
+        <v>508.205</v>
       </c>
       <c r="BB18" t="n">
-        <v>353</v>
+        <v>42.91123832983616</v>
       </c>
       <c r="BC18" t="n">
-        <v>353</v>
+        <v>43.07646947258122</v>
       </c>
       <c r="BD18" t="n">
-        <v>353</v>
+        <v>42.4713947851963</v>
       </c>
       <c r="BE18" t="n">
-        <v>353</v>
+        <v>42.74091599392788</v>
       </c>
       <c r="BF18" t="n">
-        <v>353</v>
+        <v>43.12752086029935</v>
       </c>
       <c r="BG18" t="n">
-        <v>353</v>
+        <v>43.18109173785986</v>
       </c>
       <c r="BH18" t="n">
-        <v>353</v>
+        <v>43.58537553970942</v>
       </c>
       <c r="BI18" t="n">
-        <v>353</v>
+        <v>43.82745911913564</v>
       </c>
       <c r="BJ18" t="n">
-        <v>353</v>
+        <v>44.03831258120593</v>
       </c>
       <c r="BK18" t="n">
-        <v>566</v>
+        <v>412</v>
       </c>
       <c r="BL18" t="n">
-        <v>571</v>
+        <v>412</v>
       </c>
       <c r="BM18" t="n">
-        <v>571</v>
+        <v>412</v>
       </c>
       <c r="BN18" t="n">
-        <v>571</v>
+        <v>412</v>
       </c>
       <c r="BO18" t="n">
-        <v>571</v>
+        <v>412</v>
       </c>
       <c r="BP18" t="n">
-        <v>571</v>
+        <v>412</v>
       </c>
       <c r="BQ18" t="n">
-        <v>571</v>
+        <v>412</v>
       </c>
       <c r="BR18" t="n">
-        <v>571</v>
+        <v>412</v>
       </c>
       <c r="BS18" t="n">
-        <v>571</v>
+        <v>412</v>
       </c>
       <c r="BT18" t="n">
-        <v>0.5</v>
+        <v>654</v>
       </c>
       <c r="BU18" t="n">
-        <v>1</v>
+        <v>654</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.2307692307692308</v>
+        <v>654</v>
       </c>
       <c r="BW18" t="n">
+        <v>654</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>654</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>654</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>654</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>654</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>654</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CF18" t="n">
         <v>0.7368421052631579</v>
       </c>
-      <c r="BX18" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>0.78125</v>
-      </c>
-      <c r="CB18" t="n">
-        <v>0.7368421052631579</v>
+      <c r="CG18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0.7105263157894737</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>503.59</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>44.75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S17_G5_502_38_ABS1</t>
+          <t>S18_G5_500_42_ABS1</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C19" t="n">
-        <v>38</v>
+        <v>62.26834692364714</v>
       </c>
       <c r="D19" t="n">
-        <v>56.33802816901409</v>
+        <v>42</v>
       </c>
       <c r="E19" t="n">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F19" t="n">
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>75</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>502.2027019045343</v>
-      </c>
-      <c r="J19" t="n">
-        <v>26.83959250294909</v>
-      </c>
-      <c r="K19" t="n">
-        <v>506.5814601085093</v>
-      </c>
-      <c r="L19" t="n">
-        <v>38.31113954722261</v>
-      </c>
-      <c r="M19" t="n">
-        <v>508.9145616985349</v>
-      </c>
-      <c r="N19" t="n">
-        <v>33.31055326060403</v>
-      </c>
-      <c r="O19" t="n">
-        <v>513.5157985260101</v>
-      </c>
-      <c r="P19" t="n">
-        <v>40.43809862442428</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>515.2266408298461</v>
-      </c>
       <c r="R19" t="n">
-        <v>42.36677831010575</v>
+        <v>494.01</v>
       </c>
       <c r="S19" t="n">
-        <v>512.8373153656768</v>
+        <v>45.34</v>
       </c>
       <c r="T19" t="n">
-        <v>41.01263524697738</v>
+        <v>494.99</v>
       </c>
       <c r="U19" t="n">
-        <v>510.7147086774138</v>
+        <v>48.13</v>
       </c>
       <c r="V19" t="n">
-        <v>41.64634866435404</v>
+        <v>492.58</v>
       </c>
       <c r="W19" t="n">
-        <v>506.6176020478829</v>
+        <v>49.37</v>
       </c>
       <c r="X19" t="n">
-        <v>45.03971552929563</v>
+        <v>499.66</v>
       </c>
       <c r="Y19" t="n">
-        <v>503.5873870788251</v>
+        <v>45.11</v>
       </c>
       <c r="Z19" t="n">
-        <v>44.75306935412296</v>
+        <v>498.19</v>
       </c>
       <c r="AA19" t="n">
+        <v>41.98</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>499.39</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>43.97</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>496.3</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>45.44</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>496.75</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>499.27</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>51.82</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AB19" t="n">
-        <v>0.06666666666666667</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0.06666666666666667</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0.05714285714285714</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>500.975</v>
-      </c>
       <c r="AK19" t="n">
-        <v>507.4666666666666</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="AL19" t="n">
-        <v>507.675</v>
+        <v>-0.05</v>
       </c>
       <c r="AM19" t="n">
-        <v>510.29</v>
+        <v>-0.06</v>
       </c>
       <c r="AN19" t="n">
-        <v>511.0166666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="AO19" t="n">
-        <v>511.8785714285714</v>
+        <v>-0.05714285714285714</v>
       </c>
       <c r="AP19" t="n">
-        <v>511.09375</v>
+        <v>-0.0375</v>
       </c>
       <c r="AQ19" t="n">
-        <v>509.3777777777778</v>
+        <v>-0.04444444444444445</v>
       </c>
       <c r="AR19" t="n">
-        <v>508.205</v>
+        <v>-0.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>42.91123832983616</v>
+        <v>492.975</v>
       </c>
       <c r="AT19" t="n">
-        <v>43.07646947258122</v>
+        <v>490.9333333333333</v>
       </c>
       <c r="AU19" t="n">
-        <v>42.4713947851963</v>
+        <v>492.3125</v>
       </c>
       <c r="AV19" t="n">
-        <v>42.74091599392788</v>
+        <v>493.06</v>
       </c>
       <c r="AW19" t="n">
-        <v>43.12752086029935</v>
+        <v>493.1916666666667</v>
       </c>
       <c r="AX19" t="n">
-        <v>43.18109173785986</v>
+        <v>494.9</v>
       </c>
       <c r="AY19" t="n">
-        <v>43.58537553970942</v>
+        <v>495.9875</v>
       </c>
       <c r="AZ19" t="n">
-        <v>43.82745911913564</v>
+        <v>495.4833333333333</v>
       </c>
       <c r="BA19" t="n">
-        <v>44.03831258120593</v>
+        <v>497.805</v>
       </c>
       <c r="BB19" t="n">
-        <v>412</v>
+        <v>49.66814245570293</v>
       </c>
       <c r="BC19" t="n">
-        <v>412</v>
+        <v>53.36973757560448</v>
       </c>
       <c r="BD19" t="n">
-        <v>412</v>
+        <v>53.47770417426313</v>
       </c>
       <c r="BE19" t="n">
-        <v>412</v>
+        <v>52.42782085877688</v>
       </c>
       <c r="BF19" t="n">
-        <v>412</v>
+        <v>50.08081732448951</v>
       </c>
       <c r="BG19" t="n">
-        <v>412</v>
+        <v>48.80124412933986</v>
       </c>
       <c r="BH19" t="n">
-        <v>412</v>
+        <v>48.36075210074797</v>
       </c>
       <c r="BI19" t="n">
-        <v>412</v>
+        <v>47.86804489659278</v>
       </c>
       <c r="BJ19" t="n">
-        <v>412</v>
+        <v>48.52573518247817</v>
       </c>
       <c r="BK19" t="n">
-        <v>654</v>
+        <v>353</v>
       </c>
       <c r="BL19" t="n">
-        <v>654</v>
+        <v>353</v>
       </c>
       <c r="BM19" t="n">
-        <v>654</v>
+        <v>353</v>
       </c>
       <c r="BN19" t="n">
-        <v>654</v>
+        <v>353</v>
       </c>
       <c r="BO19" t="n">
-        <v>654</v>
+        <v>353</v>
       </c>
       <c r="BP19" t="n">
-        <v>654</v>
+        <v>353</v>
       </c>
       <c r="BQ19" t="n">
-        <v>654</v>
+        <v>353</v>
       </c>
       <c r="BR19" t="n">
-        <v>654</v>
+        <v>353</v>
       </c>
       <c r="BS19" t="n">
-        <v>654</v>
+        <v>353</v>
       </c>
       <c r="BT19" t="n">
-        <v>0.1428571428571428</v>
+        <v>566</v>
       </c>
       <c r="BU19" t="n">
-        <v>0.6153846153846154</v>
+        <v>571</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.75</v>
+        <v>571</v>
       </c>
       <c r="BW19" t="n">
+        <v>571</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>571</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>571</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>571</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>571</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>571</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="CF19" t="n">
         <v>0.7368421052631579</v>
       </c>
-      <c r="BX19" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="BZ19" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="CA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB19" t="n">
-        <v>0.7105263157894737</v>
+      <c r="CG19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>0.78125</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>499.27</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>51.82</v>
       </c>
     </row>
     <row r="20">
@@ -5268,10 +5917,10 @@
         <v>501</v>
       </c>
       <c r="C20" t="n">
+        <v>57.82060785767235</v>
+      </c>
+      <c r="D20" t="n">
         <v>39</v>
-      </c>
-      <c r="D20" t="n">
-        <v>57.82060785767235</v>
       </c>
       <c r="E20" t="n">
         <v>501</v>
@@ -5280,228 +5929,261 @@
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>513.678855529977</v>
-      </c>
-      <c r="J20" t="n">
-        <v>37.16696822658414</v>
-      </c>
-      <c r="K20" t="n">
-        <v>508.7286700661702</v>
-      </c>
-      <c r="L20" t="n">
-        <v>44.91016565405874</v>
-      </c>
-      <c r="M20" t="n">
-        <v>509.1600326961156</v>
-      </c>
-      <c r="N20" t="n">
-        <v>45.86852493238505</v>
-      </c>
-      <c r="O20" t="n">
-        <v>509.7614680894617</v>
-      </c>
-      <c r="P20" t="n">
-        <v>45.66049131806494</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>508.9668295802226</v>
-      </c>
       <c r="R20" t="n">
-        <v>45.87470630863224</v>
+        <v>513.6799999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>509.1997694132165</v>
+        <v>37.17</v>
       </c>
       <c r="T20" t="n">
-        <v>45.61784214706157</v>
+        <v>508.73</v>
       </c>
       <c r="U20" t="n">
-        <v>509.9526245879338</v>
+        <v>44.91</v>
       </c>
       <c r="V20" t="n">
-        <v>49.44122764639832</v>
+        <v>509.16</v>
       </c>
       <c r="W20" t="n">
-        <v>508.9303068692274</v>
+        <v>45.87</v>
       </c>
       <c r="X20" t="n">
-        <v>47.07803215042623</v>
+        <v>509.76</v>
       </c>
       <c r="Y20" t="n">
-        <v>508.7603476983089</v>
+        <v>45.66</v>
       </c>
       <c r="Z20" t="n">
-        <v>46.2984093588841</v>
+        <v>508.97</v>
       </c>
       <c r="AA20" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>509.2</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>45.62</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>509.95</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>508.93</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>508.76</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>0.15</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AK20" t="n">
         <v>0.06666666666666667</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AL20" t="n">
         <v>0.075</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AM20" t="n">
         <v>0.06</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AN20" t="n">
         <v>0.05</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AO20" t="n">
         <v>0.04285714285714286</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AP20" t="n">
         <v>0.0375</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AQ20" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AR20" t="n">
         <v>0.03</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AS20" t="n">
         <v>515.025</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AT20" t="n">
         <v>513</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AU20" t="n">
         <v>511.95</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AV20" t="n">
         <v>512.04</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AW20" t="n">
         <v>510.875</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AX20" t="n">
         <v>510.85</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AY20" t="n">
         <v>510.1</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AZ20" t="n">
         <v>510.2111111111111</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="BA20" t="n">
         <v>509.92</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="BB20" t="n">
         <v>43.49855601051603</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="BC20" t="n">
         <v>46.38210861959598</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="BD20" t="n">
         <v>46.49809135867837</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="BE20" t="n">
         <v>47.67974832148341</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="BF20" t="n">
         <v>47.43479076585033</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="BG20" t="n">
         <v>47.23738304714664</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BH20" t="n">
         <v>47.51818073116857</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BI20" t="n">
         <v>47.43170398804872</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BJ20" t="n">
         <v>47.19993220334114</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BK20" t="n">
         <v>458</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BL20" t="n">
         <v>442</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BM20" t="n">
         <v>441</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BN20" t="n">
         <v>441</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BO20" t="n">
         <v>441</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BP20" t="n">
         <v>441</v>
       </c>
-      <c r="BH20" t="n">
+      <c r="BQ20" t="n">
         <v>441</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BR20" t="n">
         <v>441</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BS20" t="n">
         <v>441</v>
       </c>
-      <c r="BK20" t="n">
+      <c r="BT20" t="n">
         <v>631</v>
       </c>
-      <c r="BL20" t="n">
+      <c r="BU20" t="n">
         <v>631</v>
       </c>
-      <c r="BM20" t="n">
+      <c r="BV20" t="n">
         <v>631</v>
       </c>
-      <c r="BN20" t="n">
+      <c r="BW20" t="n">
         <v>631</v>
       </c>
-      <c r="BO20" t="n">
+      <c r="BX20" t="n">
         <v>631</v>
       </c>
-      <c r="BP20" t="n">
+      <c r="BY20" t="n">
         <v>631</v>
       </c>
-      <c r="BQ20" t="n">
+      <c r="BZ20" t="n">
         <v>631</v>
       </c>
-      <c r="BR20" t="n">
+      <c r="CA20" t="n">
         <v>631</v>
       </c>
-      <c r="BS20" t="n">
+      <c r="CB20" t="n">
         <v>631</v>
       </c>
-      <c r="BT20" t="n">
+      <c r="CC20" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BU20" t="n">
+      <c r="CD20" t="n">
         <v>1</v>
       </c>
-      <c r="BV20" t="n">
+      <c r="CE20" t="n">
         <v>1</v>
       </c>
-      <c r="BW20" t="n">
+      <c r="CF20" t="n">
         <v>0.9375</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="CG20" t="n">
         <v>0.2631578947368421</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CH20" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CI20" t="n">
         <v>0.8518518518518519</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CJ20" t="n">
         <v>0.896551724137931</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CK20" t="n">
         <v>0.9117647058823529</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>508.76</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>46.3</v>
       </c>
     </row>
     <row r="21">
@@ -5514,10 +6196,10 @@
         <v>498</v>
       </c>
       <c r="C21" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D21" t="n">
         <v>42</v>
-      </c>
-      <c r="D21" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E21" t="n">
         <v>498</v>
@@ -5526,228 +6208,261 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>74.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>511.3630230015949</v>
-      </c>
-      <c r="J21" t="n">
-        <v>31.69505002049259</v>
-      </c>
-      <c r="K21" t="n">
-        <v>513.258651007396</v>
-      </c>
-      <c r="L21" t="n">
-        <v>34.59906574179046</v>
-      </c>
-      <c r="M21" t="n">
-        <v>517.154399864046</v>
-      </c>
-      <c r="N21" t="n">
-        <v>34.78830608644777</v>
-      </c>
-      <c r="O21" t="n">
-        <v>516.6746027429791</v>
-      </c>
-      <c r="P21" t="n">
-        <v>33.94764863076958</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>506.5362951778498</v>
-      </c>
       <c r="R21" t="n">
-        <v>45.25127430718479</v>
+        <v>511.36</v>
       </c>
       <c r="S21" t="n">
-        <v>505.669450206682</v>
+        <v>31.7</v>
       </c>
       <c r="T21" t="n">
-        <v>47.58799048480424</v>
+        <v>513.26</v>
       </c>
       <c r="U21" t="n">
-        <v>509.0541888687403</v>
+        <v>34.6</v>
       </c>
       <c r="V21" t="n">
-        <v>49.97143006168744</v>
+        <v>517.15</v>
       </c>
       <c r="W21" t="n">
-        <v>504.0784636590216</v>
+        <v>34.79</v>
       </c>
       <c r="X21" t="n">
-        <v>54.84405832565577</v>
+        <v>516.67</v>
       </c>
       <c r="Y21" t="n">
-        <v>505.7067566494903</v>
+        <v>33.95</v>
       </c>
       <c r="Z21" t="n">
-        <v>51.84048491589045</v>
+        <v>506.54</v>
       </c>
       <c r="AA21" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>505.67</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>47.59</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>509.05</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>49.97</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>504.08</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>505.71</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>51.84</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>0.2</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AK21" t="n">
         <v>0.1186440677966102</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AL21" t="n">
         <v>0.1139240506329114</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AM21" t="n">
         <v>0.09090909090909091</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AN21" t="n">
         <v>0.008403361344537815</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AO21" t="n">
         <v>-0.05035971223021583</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AP21" t="n">
         <v>-0.03144654088050314</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AQ21" t="n">
         <v>-0.08379888268156424</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AR21" t="n">
         <v>-0.06532663316582915</v>
       </c>
-      <c r="AJ21" t="n">
+      <c r="AS21" t="n">
         <v>513.6</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
         <v>512.6666666666666</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AU21" t="n">
         <v>514.4625</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AV21" t="n">
         <v>514.63</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AW21" t="n">
         <v>512.675</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AX21" t="n">
         <v>508.7142857142857</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AY21" t="n">
         <v>509.19375</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
         <v>505.7055555555556</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
         <v>506.015</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BB21" t="n">
         <v>48.00562467044877</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BC21" t="n">
         <v>44.26837346107138</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="BD21" t="n">
         <v>43.32001377827574</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="BE21" t="n">
         <v>42.00229874661624</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BF21" t="n">
         <v>41.39749640175518</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="BG21" t="n">
         <v>43.66255108610741</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BH21" t="n">
         <v>45.29327997548312</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BI21" t="n">
         <v>46.95952124758588</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BJ21" t="n">
         <v>48.41089520965296</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BK21" t="n">
         <v>364</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BL21" t="n">
         <v>364</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BM21" t="n">
         <v>364</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BN21" t="n">
         <v>364</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BO21" t="n">
         <v>364</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BP21" t="n">
         <v>364</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BQ21" t="n">
         <v>364</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BR21" t="n">
         <v>364</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BS21" t="n">
         <v>364</v>
       </c>
-      <c r="BK21" t="n">
+      <c r="BT21" t="n">
         <v>630</v>
       </c>
-      <c r="BL21" t="n">
+      <c r="BU21" t="n">
         <v>630</v>
       </c>
-      <c r="BM21" t="n">
+      <c r="BV21" t="n">
         <v>630</v>
       </c>
-      <c r="BN21" t="n">
+      <c r="BW21" t="n">
         <v>630</v>
       </c>
-      <c r="BO21" t="n">
+      <c r="BX21" t="n">
         <v>630</v>
       </c>
-      <c r="BP21" t="n">
+      <c r="BY21" t="n">
         <v>630</v>
       </c>
-      <c r="BQ21" t="n">
+      <c r="BZ21" t="n">
         <v>630</v>
       </c>
-      <c r="BR21" t="n">
+      <c r="CA21" t="n">
         <v>630</v>
       </c>
-      <c r="BS21" t="n">
+      <c r="CB21" t="n">
         <v>630</v>
       </c>
-      <c r="BT21" t="n">
+      <c r="CC21" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BU21" t="n">
+      <c r="CD21" t="n">
         <v>0.8</v>
       </c>
-      <c r="BV21" t="n">
+      <c r="CE21" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BW21" t="n">
+      <c r="CF21" t="n">
         <v>0.8</v>
       </c>
-      <c r="BX21" t="n">
+      <c r="CG21" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="CH21" t="n">
         <v>0</v>
       </c>
-      <c r="BZ21" t="n">
+      <c r="CI21" t="n">
         <v>0.9615384615384616</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CJ21" t="n">
         <v>0.9629629629629629</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CK21" t="n">
         <v>0.8387096774193549</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>505.71</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>51.84</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>499.75</v>
       </c>
       <c r="C22" t="n">
+        <v>58.93254262416605</v>
+      </c>
+      <c r="D22" t="n">
         <v>39.75</v>
-      </c>
-      <c r="D22" t="n">
-        <v>58.93254262416605</v>
       </c>
       <c r="E22" t="n">
         <v>499.75</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.50275</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>76.2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.7275</v>
+      </c>
       <c r="I22" t="n">
-        <v>500.5861159567204</v>
+        <v>2.699</v>
       </c>
       <c r="J22" t="n">
-        <v>41.3128427873371</v>
+        <v>2.664500000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>501.1613851536158</v>
+        <v>2.6435</v>
       </c>
       <c r="L22" t="n">
-        <v>44.13075401827596</v>
+        <v>2.623</v>
       </c>
       <c r="M22" t="n">
-        <v>502.4971704913948</v>
+        <v>2.5975</v>
       </c>
       <c r="N22" t="n">
-        <v>44.14632678287167</v>
+        <v>2.656</v>
       </c>
       <c r="O22" t="n">
-        <v>502.8031194656547</v>
+        <v>2.7405</v>
       </c>
       <c r="P22" t="n">
-        <v>44.95969403154901</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>502.3449133382007</v>
-      </c>
+        <v>2.732</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>45.25869780723713</v>
+        <v>500.5860000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>501.8233977456216</v>
+        <v>41.313</v>
       </c>
       <c r="T22" t="n">
-        <v>45.72090063121612</v>
+        <v>501.1615</v>
       </c>
       <c r="U22" t="n">
-        <v>501.7829092151841</v>
+        <v>44.13</v>
       </c>
       <c r="V22" t="n">
-        <v>47.04385078604965</v>
+        <v>502.4974999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>500.7270897738936</v>
+        <v>44.1465</v>
       </c>
       <c r="X22" t="n">
-        <v>47.13496172174915</v>
+        <v>502.802</v>
       </c>
       <c r="Y22" t="n">
-        <v>500.8078692377694</v>
+        <v>44.959</v>
       </c>
       <c r="Z22" t="n">
-        <v>47.27174975846719</v>
+        <v>502.3455</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.05847165991902835</v>
+        <v>45.259</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.02203682057276447</v>
+        <v>501.823</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.00425838402104225</v>
+        <v>45.72150000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.005411831336720881</v>
+        <v>501.7819999999999</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.0015031584124306</v>
+        <v>47.044</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0.004984401652183267</v>
+        <v>500.7265</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.004327559851871905</v>
+        <v>47.13450000000001</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.01223483251276308</v>
+        <v>500.809</v>
       </c>
       <c r="AI22" t="n">
-        <v>-0.009005167224627473</v>
+        <v>47.2715</v>
       </c>
       <c r="AJ22" t="n">
-        <v>500.20125</v>
+        <v>-0.05800000000000001</v>
       </c>
       <c r="AK22" t="n">
-        <v>501.0891666666666</v>
+        <v>-0.02099999999999999</v>
       </c>
       <c r="AL22" t="n">
-        <v>502.1625</v>
+        <v>0.002499999999999999</v>
       </c>
       <c r="AM22" t="n">
+        <v>0.005499999999999999</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>-0.001499999999999998</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>-0.004999999999999999</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>-0.002999999999999997</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>-0.0095</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>500.2020000000001</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>501.09</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>502.1629999999999</v>
+      </c>
+      <c r="AV22" t="n">
         <v>502.6579999999999</v>
       </c>
-      <c r="AN22" t="n">
-        <v>502.3395833333333</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>502.0607142857143</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>501.9193750000001</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>501.3216666666667</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>501.3917499999999</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>45.3703072734054</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>47.85860189940843</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>48.24220949455633</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>48.36544967378334</v>
-      </c>
       <c r="AW22" t="n">
-        <v>48.15588049928608</v>
+        <v>502.34</v>
       </c>
       <c r="AX22" t="n">
-        <v>48.01874720705177</v>
+        <v>502.0604999999999</v>
       </c>
       <c r="AY22" t="n">
-        <v>48.08106670947757</v>
+        <v>501.9195000000001</v>
       </c>
       <c r="AZ22" t="n">
-        <v>48.14355769650803</v>
+        <v>501.3224999999999</v>
       </c>
       <c r="BA22" t="n">
-        <v>48.14300031026031</v>
+        <v>501.391</v>
       </c>
       <c r="BB22" t="n">
+        <v>45.37049999999999</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>47.858</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>48.243</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>48.36649999999999</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>48.156</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>48.01899999999999</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>48.0815</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>48.143</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>48.1435</v>
+      </c>
+      <c r="BK22" t="n">
         <v>389.55</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>387.1</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>386.75</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>386.5</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>385.65</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>384.65</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>384.1</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>383.5</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>383.5</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BT22" t="n">
         <v>605.45</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BU22" t="n">
         <v>609.7</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BV22" t="n">
         <v>610.95</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BW22" t="n">
         <v>610.95</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BX22" t="n">
         <v>610.95</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BY22" t="n">
         <v>611.05</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BZ22" t="n">
         <v>611.05</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="CA22" t="n">
         <v>611.05</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="CB22" t="n">
         <v>611.05</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0.633001443001443</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0.7582871295371295</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0.7780209373959374</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0.8151023226429572</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0.8045422679521315</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0.7017484938995237</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0.7382910216553394</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0.796750795503973</v>
-      </c>
-      <c r="CB22" t="n">
-        <v>0.799762083208141</v>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>500.809</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>47.2715</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.332784974957958</v>
       </c>
       <c r="C23" t="n">
+        <v>2.033664317415961</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.371706582097068</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.033664317415961</v>
       </c>
       <c r="E23" t="n">
         <v>1.332784974957958</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01758251224490134</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>1.567767437103509</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1537556160720128</v>
+      </c>
       <c r="I23" t="n">
-        <v>11.37897749993849</v>
+        <v>0.163800263478999</v>
       </c>
       <c r="J23" t="n">
-        <v>18.30882267911187</v>
+        <v>0.1584289646564203</v>
       </c>
       <c r="K23" t="n">
-        <v>11.03775305573707</v>
+        <v>0.1507970054149128</v>
       </c>
       <c r="L23" t="n">
-        <v>14.07911660340616</v>
+        <v>0.1551264340024479</v>
       </c>
       <c r="M23" t="n">
-        <v>9.976319334431549</v>
+        <v>0.1568732307511891</v>
       </c>
       <c r="N23" t="n">
-        <v>9.407076483797942</v>
+        <v>0.290940399032987</v>
       </c>
       <c r="O23" t="n">
-        <v>9.271719019941765</v>
+        <v>0.1578965350774794</v>
       </c>
       <c r="P23" t="n">
-        <v>7.871561497489295</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>7.597533243256247</v>
-      </c>
+        <v>0.1396838535671479</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>6.947815524625073</v>
+        <v>11.37858209647914</v>
       </c>
       <c r="S23" t="n">
-        <v>6.534063535939259</v>
+        <v>18.30834468932563</v>
       </c>
       <c r="T23" t="n">
-        <v>6.588826664488049</v>
+        <v>11.03756326798341</v>
       </c>
       <c r="U23" t="n">
-        <v>6.37948735032994</v>
+        <v>14.07915031826177</v>
       </c>
       <c r="V23" t="n">
-        <v>6.956529862861727</v>
+        <v>9.975566927564358</v>
       </c>
       <c r="W23" t="n">
-        <v>5.512928630659053</v>
+        <v>9.407668358704425</v>
       </c>
       <c r="X23" t="n">
-        <v>6.610552702037694</v>
+        <v>9.272534201949089</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.835071605056417</v>
+        <v>7.87059744940156</v>
       </c>
       <c r="Z23" t="n">
-        <v>6.022785130734515</v>
+        <v>7.597477749746606</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.2526214116360915</v>
+        <v>6.947332619524977</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.1666205178635343</v>
+        <v>6.533964783305294</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.1285392897981993</v>
+        <v>6.588831279641249</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.09740787472015675</v>
+        <v>6.379036884902562</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.07190754215070985</v>
+        <v>6.955738562321648</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.06247286387380184</v>
+        <v>5.51320546267634</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.06057678796665939</v>
+        <v>6.610724520369194</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.0556933192768468</v>
+        <v>4.835107248579207</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.05065360313576373</v>
+        <v>6.024042422266229</v>
       </c>
       <c r="AJ23" t="n">
-        <v>11.77571786559104</v>
+        <v>0.2529322771852285</v>
       </c>
       <c r="AK23" t="n">
-        <v>11.24993732926015</v>
+        <v>0.1682072656294202</v>
       </c>
       <c r="AL23" t="n">
-        <v>10.45551824837513</v>
+        <v>0.1288767260847194</v>
       </c>
       <c r="AM23" t="n">
+        <v>0.09730445978852584</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.07220402379806529</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0.06295361701075516</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.06070636834710784</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.05502152688768853</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0.05195899192733885</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>11.77488969665623</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>11.25028748170698</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>10.45512923728928</v>
+      </c>
+      <c r="AV23" t="n">
         <v>9.905762065851528</v>
       </c>
-      <c r="AN23" t="n">
-        <v>8.982089828249794</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>7.866727407722433</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>7.302051098609937</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>6.731112940406254</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>6.362484262207814</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>10.68468218214513</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>10.3281630704591</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>9.942378624821332</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>8.514223261091784</v>
-      </c>
       <c r="AW23" t="n">
-        <v>7.45893311355927</v>
+        <v>8.981608108269155</v>
       </c>
       <c r="AX23" t="n">
-        <v>6.673093795810321</v>
+        <v>7.867248883822095</v>
       </c>
       <c r="AY23" t="n">
-        <v>6.210343320772251</v>
+        <v>7.302659555185864</v>
       </c>
       <c r="AZ23" t="n">
-        <v>5.964584168541496</v>
+        <v>6.731486013308539</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.769717440520642</v>
+        <v>6.361457049251666</v>
       </c>
       <c r="BB23" t="n">
+        <v>10.6854172516615</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>10.32796235061832</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>9.942608521435726</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>8.514438681007197</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>7.458771170133929</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>6.673350693143902</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>6.211035403978445</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>5.964382087375903</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>5.769852935278061</v>
+      </c>
+      <c r="BK23" t="n">
         <v>40.40775720211731</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>37.7915334433521</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BM23" t="n">
         <v>37.2090467211233</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BN23" t="n">
         <v>36.6828512924959</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BO23" t="n">
         <v>35.1167601311007</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BP23" t="n">
         <v>33.49198647280775</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BQ23" t="n">
         <v>32.755714648062</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>32.1485040987831</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>32.1485040987831</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BT23" t="n">
         <v>37.43271156003586</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BU23" t="n">
         <v>32.1773048493565</v>
       </c>
-      <c r="BM23" t="n">
+      <c r="BV23" t="n">
         <v>30.36700945364714</v>
       </c>
-      <c r="BN23" t="n">
+      <c r="BW23" t="n">
         <v>30.36700945364714</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BX23" t="n">
         <v>30.36700945364714</v>
       </c>
-      <c r="BP23" t="n">
+      <c r="BY23" t="n">
         <v>30.2036508772663</v>
       </c>
-      <c r="BQ23" t="n">
+      <c r="BZ23" t="n">
         <v>30.2036508772663</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="CA23" t="n">
         <v>30.2036508772663</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="CB23" t="n">
         <v>30.2036508772663</v>
       </c>
-      <c r="BT23" t="n">
-        <v>0.2640550457438797</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>0.252540808302857</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>0.2886697617320565</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0.1060031312119252</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>0.1459068070885773</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>0.3121860577288796</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0.2634507629356792</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>0.2321502991010069</v>
-      </c>
-      <c r="CB23" t="n">
-        <v>0.2356185590897906</v>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>4.835107248579207</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>6.024042422266229</v>
       </c>
     </row>
   </sheetData>
